--- a/excel/Salida.xlsx
+++ b/excel/Salida.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Developer\VacacionesOthman\GeoSupport\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EA2F1C-67F2-4038-BCDC-69CACCCDDBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -826,11 +832,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -894,13 +900,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -938,7 +952,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -972,6 +986,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1006,9 +1021,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1181,2156 +1197,2099 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="82" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="186.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="99.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="62.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="64.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="62.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="94" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="64.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="132.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
-      <c r="A2" s="1">
-        <v>0</v>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2">
+        <v>79.159000000000006</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46178.48945601852</v>
+      </c>
+      <c r="H2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K2" t="s">
+        <v>194</v>
+      </c>
+      <c r="L2" t="s">
+        <v>203</v>
+      </c>
+      <c r="M2" t="s">
+        <v>231</v>
+      </c>
+      <c r="N2" t="s">
+        <v>232</v>
+      </c>
+      <c r="P2" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>234</v>
+      </c>
+      <c r="R2" t="s">
+        <v>235</v>
+      </c>
+      <c r="S2" t="s">
+        <v>236</v>
+      </c>
+      <c r="T2" t="s">
+        <v>194</v>
+      </c>
+      <c r="U2" t="s">
+        <v>166</v>
+      </c>
+      <c r="V2" t="s">
+        <v>241</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
         <v>81</v>
       </c>
-      <c r="E2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G2">
-        <v>79.15900000000001</v>
-      </c>
-      <c r="H2" s="2">
-        <v>46178.48945601852</v>
-      </c>
-      <c r="I2" t="s">
-        <v>138</v>
-      </c>
-      <c r="J2" t="s">
-        <v>166</v>
-      </c>
-      <c r="K2" t="s">
-        <v>138</v>
-      </c>
-      <c r="L2" t="s">
-        <v>194</v>
-      </c>
-      <c r="M2" t="s">
-        <v>203</v>
-      </c>
-      <c r="N2" t="s">
-        <v>231</v>
-      </c>
-      <c r="O2" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>233</v>
-      </c>
-      <c r="R2" t="s">
-        <v>234</v>
-      </c>
-      <c r="S2" t="s">
-        <v>235</v>
-      </c>
-      <c r="T2" t="s">
-        <v>236</v>
-      </c>
-      <c r="U2" t="s">
-        <v>194</v>
-      </c>
-      <c r="V2" t="s">
-        <v>166</v>
-      </c>
-      <c r="W2" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" t="s">
         <v>111</v>
       </c>
-      <c r="G3">
+      <c r="F3">
         <v>11.012</v>
       </c>
-      <c r="H3" s="2">
+      <c r="G3" s="2">
         <v>46178.48946759259</v>
       </c>
+      <c r="H3" t="s">
+        <v>139</v>
+      </c>
       <c r="I3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J3" t="s">
         <v>139</v>
       </c>
-      <c r="J3" t="s">
-        <v>167</v>
-      </c>
       <c r="K3" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="L3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="M3" t="s">
         <v>204</v>
       </c>
       <c r="N3" t="s">
-        <v>204</v>
-      </c>
-      <c r="O3" t="s">
         <v>139</v>
       </c>
+      <c r="P3" t="s">
+        <v>233</v>
+      </c>
       <c r="Q3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T3" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="U3" t="s">
+        <v>167</v>
+      </c>
+      <c r="V3" t="s">
+        <v>242</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4">
+        <v>762.00099999999998</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46178.489548611113</v>
+      </c>
+      <c r="H4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I4" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" t="s">
+        <v>140</v>
+      </c>
+      <c r="K4" t="s">
         <v>195</v>
       </c>
-      <c r="V3" t="s">
-        <v>167</v>
-      </c>
-      <c r="W3" t="s">
-        <v>242</v>
-      </c>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4">
-        <v>762.001</v>
-      </c>
-      <c r="H4" s="2">
-        <v>46178.48954861111</v>
-      </c>
-      <c r="I4" t="s">
-        <v>140</v>
-      </c>
-      <c r="J4" t="s">
-        <v>168</v>
-      </c>
-      <c r="K4" t="s">
-        <v>140</v>
-      </c>
       <c r="L4" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="M4" t="s">
         <v>205</v>
       </c>
       <c r="N4" t="s">
-        <v>205</v>
-      </c>
-      <c r="O4" t="s">
         <v>140</v>
       </c>
+      <c r="P4" t="s">
+        <v>233</v>
+      </c>
       <c r="Q4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T4" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="U4" t="s">
+        <v>168</v>
+      </c>
+      <c r="V4" t="s">
+        <v>243</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5">
+        <v>640.96500000000003</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46178.489710648151</v>
+      </c>
+      <c r="H5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K5" t="s">
         <v>195</v>
       </c>
-      <c r="V4" t="s">
-        <v>168</v>
-      </c>
-      <c r="W4" t="s">
-        <v>243</v>
-      </c>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G5">
-        <v>640.965</v>
-      </c>
-      <c r="H5" s="2">
-        <v>46178.48971064815</v>
-      </c>
-      <c r="I5" t="s">
-        <v>141</v>
-      </c>
-      <c r="J5" t="s">
-        <v>169</v>
-      </c>
-      <c r="K5" t="s">
-        <v>141</v>
-      </c>
       <c r="L5" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="M5" t="s">
         <v>206</v>
       </c>
       <c r="N5" t="s">
-        <v>206</v>
-      </c>
-      <c r="O5" t="s">
         <v>141</v>
       </c>
+      <c r="P5" t="s">
+        <v>233</v>
+      </c>
       <c r="Q5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T5" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="U5" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="V5" t="s">
-        <v>169</v>
-      </c>
-      <c r="W5" t="s">
         <v>244</v>
       </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
       <c r="Y5" t="b">
         <v>0</v>
       </c>
-      <c r="Z5" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="1">
-        <v>4</v>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" t="s">
         <v>114</v>
       </c>
-      <c r="G6">
+      <c r="F6">
         <v>63.628</v>
       </c>
-      <c r="H6" s="2">
-        <v>46178.48979166667</v>
+      <c r="G6" s="2">
+        <v>46178.489791666667</v>
+      </c>
+      <c r="H6" t="s">
+        <v>142</v>
       </c>
       <c r="I6" t="s">
+        <v>170</v>
+      </c>
+      <c r="J6" t="s">
         <v>142</v>
       </c>
-      <c r="J6" t="s">
-        <v>170</v>
-      </c>
       <c r="K6" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="L6" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="M6" t="s">
         <v>207</v>
       </c>
       <c r="N6" t="s">
-        <v>207</v>
-      </c>
-      <c r="O6" t="s">
         <v>142</v>
       </c>
+      <c r="P6" t="s">
+        <v>233</v>
+      </c>
       <c r="Q6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T6" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="U6" t="s">
+        <v>170</v>
+      </c>
+      <c r="V6" t="s">
+        <v>245</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7">
+        <v>102.047</v>
+      </c>
+      <c r="G7" s="2">
+        <v>46178.489837962959</v>
+      </c>
+      <c r="H7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I7" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" t="s">
+        <v>143</v>
+      </c>
+      <c r="K7" t="s">
         <v>196</v>
       </c>
-      <c r="V6" t="s">
-        <v>170</v>
-      </c>
-      <c r="W6" t="s">
-        <v>245</v>
-      </c>
-      <c r="Y6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F7" t="s">
-        <v>115</v>
-      </c>
-      <c r="G7">
-        <v>102.047</v>
-      </c>
-      <c r="H7" s="2">
-        <v>46178.48983796296</v>
-      </c>
-      <c r="I7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J7" t="s">
-        <v>171</v>
-      </c>
-      <c r="K7" t="s">
-        <v>143</v>
-      </c>
       <c r="L7" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="M7" t="s">
         <v>208</v>
       </c>
       <c r="N7" t="s">
-        <v>208</v>
-      </c>
-      <c r="O7" t="s">
         <v>143</v>
       </c>
+      <c r="P7" t="s">
+        <v>233</v>
+      </c>
       <c r="Q7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T7" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="U7" t="s">
+        <v>171</v>
+      </c>
+      <c r="V7" t="s">
+        <v>246</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8">
+        <v>156.84399999999999</v>
+      </c>
+      <c r="G8" s="2">
+        <v>46178.489861111113</v>
+      </c>
+      <c r="H8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" t="s">
+        <v>172</v>
+      </c>
+      <c r="J8" t="s">
+        <v>144</v>
+      </c>
+      <c r="K8" t="s">
         <v>196</v>
       </c>
-      <c r="V7" t="s">
-        <v>171</v>
-      </c>
-      <c r="W7" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8">
-        <v>156.844</v>
-      </c>
-      <c r="H8" s="2">
-        <v>46178.48986111111</v>
-      </c>
-      <c r="I8" t="s">
-        <v>144</v>
-      </c>
-      <c r="J8" t="s">
-        <v>172</v>
-      </c>
-      <c r="K8" t="s">
-        <v>144</v>
-      </c>
       <c r="L8" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M8" t="s">
         <v>209</v>
       </c>
       <c r="N8" t="s">
-        <v>209</v>
-      </c>
-      <c r="O8" t="s">
         <v>144</v>
       </c>
+      <c r="P8" t="s">
+        <v>233</v>
+      </c>
       <c r="Q8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S8" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T8" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="U8" t="s">
+        <v>172</v>
+      </c>
+      <c r="V8" t="s">
+        <v>247</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9">
+        <v>71.19</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46178.489918981482</v>
+      </c>
+      <c r="H9" t="s">
+        <v>145</v>
+      </c>
+      <c r="I9" t="s">
+        <v>173</v>
+      </c>
+      <c r="J9" t="s">
+        <v>145</v>
+      </c>
+      <c r="K9" t="s">
         <v>196</v>
       </c>
-      <c r="V8" t="s">
-        <v>172</v>
-      </c>
-      <c r="W8" t="s">
-        <v>247</v>
-      </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G9">
-        <v>71.19</v>
-      </c>
-      <c r="H9" s="2">
-        <v>46178.48991898148</v>
-      </c>
-      <c r="I9" t="s">
-        <v>145</v>
-      </c>
-      <c r="J9" t="s">
-        <v>173</v>
-      </c>
-      <c r="K9" t="s">
-        <v>145</v>
-      </c>
       <c r="L9" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="M9" t="s">
         <v>210</v>
       </c>
       <c r="N9" t="s">
-        <v>210</v>
-      </c>
-      <c r="O9" t="s">
         <v>145</v>
       </c>
+      <c r="P9" t="s">
+        <v>233</v>
+      </c>
       <c r="Q9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T9" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="U9" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="V9" t="s">
-        <v>173</v>
-      </c>
-      <c r="W9" t="s">
         <v>248</v>
       </c>
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
       <c r="Y9" t="b">
         <v>0</v>
       </c>
-      <c r="Z9" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:26">
-      <c r="A10" s="1">
-        <v>8</v>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" t="s">
         <v>118</v>
       </c>
-      <c r="G10">
-        <v>3217.563</v>
-      </c>
-      <c r="H10" s="2">
-        <v>46178.49026620371</v>
+      <c r="F10">
+        <v>3217.5630000000001</v>
+      </c>
+      <c r="G10" s="2">
+        <v>46178.490266203713</v>
+      </c>
+      <c r="H10" t="s">
+        <v>146</v>
       </c>
       <c r="I10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" t="s">
         <v>146</v>
       </c>
-      <c r="J10" t="s">
-        <v>174</v>
-      </c>
       <c r="K10" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="L10" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="M10" t="s">
         <v>211</v>
       </c>
       <c r="N10" t="s">
-        <v>211</v>
-      </c>
-      <c r="O10" t="s">
         <v>146</v>
       </c>
+      <c r="P10" t="s">
+        <v>233</v>
+      </c>
       <c r="Q10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S10" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T10" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="U10" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="V10" t="s">
-        <v>174</v>
-      </c>
-      <c r="W10" t="s">
         <v>249</v>
       </c>
+      <c r="X10" t="b">
+        <v>0</v>
+      </c>
       <c r="Y10" t="b">
         <v>0</v>
       </c>
-      <c r="Z10" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:26">
-      <c r="A11" s="1">
-        <v>9</v>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" t="s">
         <v>119</v>
       </c>
-      <c r="G11">
-        <v>264.282</v>
-      </c>
-      <c r="H11" s="2">
-        <v>46178.4903587963</v>
+      <c r="F11">
+        <v>264.28199999999998</v>
+      </c>
+      <c r="G11" s="2">
+        <v>46178.490358796298</v>
+      </c>
+      <c r="H11" t="s">
+        <v>147</v>
       </c>
       <c r="I11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" t="s">
         <v>147</v>
       </c>
-      <c r="J11" t="s">
-        <v>175</v>
-      </c>
       <c r="K11" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="L11" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="M11" t="s">
         <v>212</v>
       </c>
       <c r="N11" t="s">
-        <v>212</v>
-      </c>
-      <c r="O11" t="s">
         <v>147</v>
       </c>
+      <c r="P11" t="s">
+        <v>233</v>
+      </c>
       <c r="Q11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S11" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T11" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="U11" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="V11" t="s">
-        <v>175</v>
-      </c>
-      <c r="W11" t="s">
         <v>250</v>
       </c>
+      <c r="X11" t="b">
+        <v>0</v>
+      </c>
       <c r="Y11" t="b">
         <v>0</v>
       </c>
-      <c r="Z11" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" spans="1:26">
-      <c r="A12" s="1">
-        <v>10</v>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" t="s">
         <v>120</v>
       </c>
-      <c r="G12">
+      <c r="F12">
         <v>531.553</v>
       </c>
-      <c r="H12" s="2">
-        <v>46178.49045138889</v>
+      <c r="G12" s="2">
+        <v>46178.490451388891</v>
+      </c>
+      <c r="H12" t="s">
+        <v>148</v>
       </c>
       <c r="I12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" t="s">
         <v>148</v>
       </c>
-      <c r="J12" t="s">
-        <v>176</v>
-      </c>
       <c r="K12" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="L12" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="M12" t="s">
         <v>213</v>
       </c>
       <c r="N12" t="s">
-        <v>213</v>
-      </c>
-      <c r="O12" t="s">
         <v>148</v>
       </c>
+      <c r="P12" t="s">
+        <v>233</v>
+      </c>
       <c r="Q12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T12" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="U12" t="s">
+        <v>176</v>
+      </c>
+      <c r="V12" t="s">
+        <v>251</v>
+      </c>
+      <c r="X12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13">
+        <v>399.55</v>
+      </c>
+      <c r="G13" s="2">
+        <v>46178.490555555552</v>
+      </c>
+      <c r="H13" t="s">
+        <v>149</v>
+      </c>
+      <c r="I13" t="s">
+        <v>177</v>
+      </c>
+      <c r="J13" t="s">
+        <v>149</v>
+      </c>
+      <c r="K13" t="s">
         <v>198</v>
       </c>
-      <c r="V12" t="s">
-        <v>176</v>
-      </c>
-      <c r="W12" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" t="s">
-        <v>121</v>
-      </c>
-      <c r="G13">
-        <v>399.55</v>
-      </c>
-      <c r="H13" s="2">
-        <v>46178.49055555555</v>
-      </c>
-      <c r="I13" t="s">
-        <v>149</v>
-      </c>
-      <c r="J13" t="s">
-        <v>177</v>
-      </c>
-      <c r="K13" t="s">
-        <v>149</v>
-      </c>
       <c r="L13" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="M13" t="s">
         <v>214</v>
       </c>
       <c r="N13" t="s">
-        <v>214</v>
-      </c>
-      <c r="O13" t="s">
         <v>149</v>
       </c>
+      <c r="P13" t="s">
+        <v>233</v>
+      </c>
       <c r="Q13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T13" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="U13" t="s">
+        <v>177</v>
+      </c>
+      <c r="V13" t="s">
+        <v>252</v>
+      </c>
+      <c r="X13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14">
+        <v>954.30399999999997</v>
+      </c>
+      <c r="G14" s="2">
+        <v>46178.490659722222</v>
+      </c>
+      <c r="H14" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" t="s">
+        <v>178</v>
+      </c>
+      <c r="J14" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" t="s">
         <v>198</v>
       </c>
-      <c r="V13" t="s">
-        <v>177</v>
-      </c>
-      <c r="W13" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" t="s">
-        <v>122</v>
-      </c>
-      <c r="G14">
-        <v>954.304</v>
-      </c>
-      <c r="H14" s="2">
-        <v>46178.49065972222</v>
-      </c>
-      <c r="I14" t="s">
-        <v>150</v>
-      </c>
-      <c r="J14" t="s">
-        <v>178</v>
-      </c>
-      <c r="K14" t="s">
-        <v>150</v>
-      </c>
       <c r="L14" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="M14" t="s">
         <v>215</v>
       </c>
       <c r="N14" t="s">
-        <v>215</v>
-      </c>
-      <c r="O14" t="s">
         <v>150</v>
       </c>
+      <c r="P14" t="s">
+        <v>233</v>
+      </c>
       <c r="Q14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S14" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T14" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="U14" t="s">
+        <v>178</v>
+      </c>
+      <c r="V14" t="s">
+        <v>253</v>
+      </c>
+      <c r="X14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15">
+        <v>156.93700000000001</v>
+      </c>
+      <c r="G15" s="2">
+        <v>46178.490682870368</v>
+      </c>
+      <c r="H15" t="s">
+        <v>151</v>
+      </c>
+      <c r="I15" t="s">
+        <v>179</v>
+      </c>
+      <c r="J15" t="s">
+        <v>151</v>
+      </c>
+      <c r="K15" t="s">
         <v>198</v>
       </c>
-      <c r="V14" t="s">
-        <v>178</v>
-      </c>
-      <c r="W14" t="s">
-        <v>253</v>
-      </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" t="s">
-        <v>123</v>
-      </c>
-      <c r="G15">
-        <v>156.937</v>
-      </c>
-      <c r="H15" s="2">
-        <v>46178.49068287037</v>
-      </c>
-      <c r="I15" t="s">
-        <v>151</v>
-      </c>
-      <c r="J15" t="s">
-        <v>179</v>
-      </c>
-      <c r="K15" t="s">
-        <v>151</v>
-      </c>
       <c r="L15" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="M15" t="s">
         <v>216</v>
       </c>
       <c r="N15" t="s">
-        <v>216</v>
-      </c>
-      <c r="O15" t="s">
         <v>151</v>
       </c>
+      <c r="P15" t="s">
+        <v>233</v>
+      </c>
       <c r="Q15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S15" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T15" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="U15" t="s">
+        <v>179</v>
+      </c>
+      <c r="V15" t="s">
+        <v>254</v>
+      </c>
+      <c r="X15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16">
+        <v>213.75399999999999</v>
+      </c>
+      <c r="G16" s="2">
+        <v>46178.490729166668</v>
+      </c>
+      <c r="H16" t="s">
+        <v>152</v>
+      </c>
+      <c r="I16" t="s">
+        <v>180</v>
+      </c>
+      <c r="J16" t="s">
+        <v>152</v>
+      </c>
+      <c r="K16" t="s">
         <v>198</v>
       </c>
-      <c r="V15" t="s">
-        <v>179</v>
-      </c>
-      <c r="W15" t="s">
-        <v>254</v>
-      </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16">
-        <v>213.754</v>
-      </c>
-      <c r="H16" s="2">
-        <v>46178.49072916667</v>
-      </c>
-      <c r="I16" t="s">
-        <v>152</v>
-      </c>
-      <c r="J16" t="s">
-        <v>180</v>
-      </c>
-      <c r="K16" t="s">
-        <v>152</v>
-      </c>
       <c r="L16" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="M16" t="s">
         <v>217</v>
       </c>
       <c r="N16" t="s">
-        <v>217</v>
-      </c>
-      <c r="O16" t="s">
         <v>152</v>
       </c>
+      <c r="P16" t="s">
+        <v>233</v>
+      </c>
       <c r="Q16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S16" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T16" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="U16" t="s">
+        <v>180</v>
+      </c>
+      <c r="V16" t="s">
+        <v>255</v>
+      </c>
+      <c r="X16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17">
+        <v>820.83399999999995</v>
+      </c>
+      <c r="G17" s="2">
+        <v>46178.490833333337</v>
+      </c>
+      <c r="H17" t="s">
+        <v>153</v>
+      </c>
+      <c r="I17" t="s">
+        <v>181</v>
+      </c>
+      <c r="J17" t="s">
+        <v>153</v>
+      </c>
+      <c r="K17" t="s">
         <v>198</v>
       </c>
-      <c r="V16" t="s">
-        <v>180</v>
-      </c>
-      <c r="W16" t="s">
-        <v>255</v>
-      </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G17">
-        <v>820.8339999999999</v>
-      </c>
-      <c r="H17" s="2">
-        <v>46178.49083333334</v>
-      </c>
-      <c r="I17" t="s">
-        <v>153</v>
-      </c>
-      <c r="J17" t="s">
-        <v>181</v>
-      </c>
-      <c r="K17" t="s">
-        <v>153</v>
-      </c>
       <c r="L17" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="M17" t="s">
         <v>218</v>
       </c>
       <c r="N17" t="s">
-        <v>218</v>
-      </c>
-      <c r="O17" t="s">
         <v>153</v>
       </c>
+      <c r="P17" t="s">
+        <v>233</v>
+      </c>
       <c r="Q17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T17" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="U17" t="s">
+        <v>181</v>
+      </c>
+      <c r="V17" t="s">
+        <v>256</v>
+      </c>
+      <c r="X17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>126</v>
+      </c>
+      <c r="F18">
+        <v>56.174999999999997</v>
+      </c>
+      <c r="G18" s="2">
+        <v>46178.490868055553</v>
+      </c>
+      <c r="H18" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" t="s">
+        <v>182</v>
+      </c>
+      <c r="J18" t="s">
+        <v>154</v>
+      </c>
+      <c r="K18" t="s">
         <v>198</v>
       </c>
-      <c r="V17" t="s">
-        <v>181</v>
-      </c>
-      <c r="W17" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" t="s">
-        <v>126</v>
-      </c>
-      <c r="G18">
-        <v>56.175</v>
-      </c>
-      <c r="H18" s="2">
-        <v>46178.49086805555</v>
-      </c>
-      <c r="I18" t="s">
-        <v>154</v>
-      </c>
-      <c r="J18" t="s">
-        <v>182</v>
-      </c>
-      <c r="K18" t="s">
-        <v>154</v>
-      </c>
       <c r="L18" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="M18" t="s">
         <v>219</v>
       </c>
       <c r="N18" t="s">
-        <v>219</v>
-      </c>
-      <c r="O18" t="s">
         <v>154</v>
       </c>
+      <c r="P18" t="s">
+        <v>233</v>
+      </c>
       <c r="Q18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S18" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T18" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="U18" t="s">
+        <v>182</v>
+      </c>
+      <c r="V18" t="s">
+        <v>257</v>
+      </c>
+      <c r="X18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19">
+        <v>29.052</v>
+      </c>
+      <c r="G19" s="2">
+        <v>46178.490891203714</v>
+      </c>
+      <c r="H19" t="s">
+        <v>155</v>
+      </c>
+      <c r="I19" t="s">
+        <v>183</v>
+      </c>
+      <c r="J19" t="s">
+        <v>155</v>
+      </c>
+      <c r="K19" t="s">
         <v>198</v>
       </c>
-      <c r="V18" t="s">
-        <v>182</v>
-      </c>
-      <c r="W18" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26">
-      <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G19">
-        <v>29.052</v>
-      </c>
-      <c r="H19" s="2">
-        <v>46178.49089120371</v>
-      </c>
-      <c r="I19" t="s">
-        <v>155</v>
-      </c>
-      <c r="J19" t="s">
-        <v>183</v>
-      </c>
-      <c r="K19" t="s">
-        <v>155</v>
-      </c>
       <c r="L19" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s">
         <v>220</v>
       </c>
       <c r="N19" t="s">
-        <v>220</v>
-      </c>
-      <c r="O19" t="s">
         <v>155</v>
       </c>
+      <c r="P19" t="s">
+        <v>233</v>
+      </c>
       <c r="Q19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S19" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T19" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="U19" t="s">
+        <v>183</v>
+      </c>
+      <c r="V19" t="s">
+        <v>258</v>
+      </c>
+      <c r="X19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20">
+        <v>1813.4090000000001</v>
+      </c>
+      <c r="G20" s="2">
+        <v>46178.491064814807</v>
+      </c>
+      <c r="H20" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" t="s">
+        <v>184</v>
+      </c>
+      <c r="J20" t="s">
+        <v>156</v>
+      </c>
+      <c r="K20" t="s">
         <v>198</v>
       </c>
-      <c r="V19" t="s">
-        <v>183</v>
-      </c>
-      <c r="W19" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26">
-      <c r="A20" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20">
-        <v>1813.409</v>
-      </c>
-      <c r="H20" s="2">
-        <v>46178.49106481481</v>
-      </c>
-      <c r="I20" t="s">
-        <v>156</v>
-      </c>
-      <c r="J20" t="s">
-        <v>184</v>
-      </c>
-      <c r="K20" t="s">
-        <v>156</v>
-      </c>
       <c r="L20" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="M20" t="s">
         <v>221</v>
       </c>
       <c r="N20" t="s">
-        <v>221</v>
-      </c>
-      <c r="O20" t="s">
         <v>156</v>
       </c>
+      <c r="P20" t="s">
+        <v>233</v>
+      </c>
       <c r="Q20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S20" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T20" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="U20" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="V20" t="s">
-        <v>184</v>
-      </c>
-      <c r="W20" t="s">
         <v>259</v>
       </c>
+      <c r="X20" t="b">
+        <v>0</v>
+      </c>
       <c r="Y20" t="b">
         <v>0</v>
       </c>
-      <c r="Z20" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="21" spans="1:26">
-      <c r="A21" s="1">
-        <v>19</v>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" t="s">
         <v>129</v>
       </c>
-      <c r="G21">
+      <c r="F21">
         <v>1021.143</v>
       </c>
-      <c r="H21" s="2">
+      <c r="G21" s="2">
         <v>46178.49119212963</v>
       </c>
+      <c r="H21" t="s">
+        <v>157</v>
+      </c>
       <c r="I21" t="s">
+        <v>185</v>
+      </c>
+      <c r="J21" t="s">
         <v>157</v>
       </c>
-      <c r="J21" t="s">
-        <v>185</v>
-      </c>
       <c r="K21" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="L21" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s">
         <v>222</v>
       </c>
       <c r="N21" t="s">
-        <v>222</v>
-      </c>
-      <c r="O21" t="s">
         <v>157</v>
       </c>
+      <c r="P21" t="s">
+        <v>233</v>
+      </c>
       <c r="Q21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R21" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S21" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T21" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="U21" t="s">
+        <v>185</v>
+      </c>
+      <c r="V21" t="s">
+        <v>260</v>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22">
+        <v>56.639000000000003</v>
+      </c>
+      <c r="G22" s="2">
+        <v>46178.491238425922</v>
+      </c>
+      <c r="H22" t="s">
+        <v>158</v>
+      </c>
+      <c r="I22" t="s">
+        <v>186</v>
+      </c>
+      <c r="J22" t="s">
+        <v>158</v>
+      </c>
+      <c r="K22" t="s">
         <v>199</v>
       </c>
-      <c r="V21" t="s">
-        <v>185</v>
-      </c>
-      <c r="W21" t="s">
-        <v>260</v>
-      </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26">
-      <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22">
-        <v>56.639</v>
-      </c>
-      <c r="H22" s="2">
-        <v>46178.49123842592</v>
-      </c>
-      <c r="I22" t="s">
-        <v>158</v>
-      </c>
-      <c r="J22" t="s">
-        <v>186</v>
-      </c>
-      <c r="K22" t="s">
-        <v>158</v>
-      </c>
       <c r="L22" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="M22" t="s">
         <v>223</v>
       </c>
       <c r="N22" t="s">
-        <v>223</v>
-      </c>
-      <c r="O22" t="s">
         <v>158</v>
       </c>
+      <c r="P22" t="s">
+        <v>233</v>
+      </c>
       <c r="Q22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S22" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T22" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="U22" t="s">
+        <v>186</v>
+      </c>
+      <c r="V22" t="s">
+        <v>261</v>
+      </c>
+      <c r="X22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23">
+        <v>2073.665</v>
+      </c>
+      <c r="G23" s="2">
+        <v>46178.49150462963</v>
+      </c>
+      <c r="H23" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" t="s">
+        <v>159</v>
+      </c>
+      <c r="K23" t="s">
         <v>199</v>
       </c>
-      <c r="V22" t="s">
-        <v>186</v>
-      </c>
-      <c r="W22" t="s">
-        <v>261</v>
-      </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" t="s">
-        <v>131</v>
-      </c>
-      <c r="G23">
-        <v>2073.665</v>
-      </c>
-      <c r="H23" s="2">
-        <v>46178.49150462963</v>
-      </c>
-      <c r="I23" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" t="s">
-        <v>187</v>
-      </c>
-      <c r="K23" t="s">
-        <v>159</v>
-      </c>
       <c r="L23" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s">
         <v>224</v>
       </c>
       <c r="N23" t="s">
-        <v>224</v>
-      </c>
-      <c r="O23" t="s">
         <v>159</v>
       </c>
+      <c r="P23" t="s">
+        <v>233</v>
+      </c>
       <c r="Q23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S23" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T23" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="U23" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="V23" t="s">
-        <v>187</v>
-      </c>
-      <c r="W23" t="s">
         <v>262</v>
       </c>
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
       <c r="Y23" t="b">
         <v>0</v>
       </c>
-      <c r="Z23" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="24" spans="1:26">
-      <c r="A24" s="1">
-        <v>25</v>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" t="s">
         <v>132</v>
       </c>
-      <c r="G24">
+      <c r="F24">
         <v>721.83</v>
       </c>
-      <c r="H24" s="2">
-        <v>46178.49165509259</v>
+      <c r="G24" s="2">
+        <v>46178.491655092592</v>
+      </c>
+      <c r="H24" t="s">
+        <v>160</v>
       </c>
       <c r="I24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J24" t="s">
         <v>160</v>
       </c>
-      <c r="J24" t="s">
-        <v>188</v>
-      </c>
       <c r="K24" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="L24" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s">
         <v>225</v>
       </c>
       <c r="N24" t="s">
-        <v>225</v>
-      </c>
-      <c r="O24" t="s">
         <v>160</v>
       </c>
+      <c r="P24" t="s">
+        <v>233</v>
+      </c>
       <c r="Q24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S24" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T24" t="s">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="U24" t="s">
+        <v>188</v>
+      </c>
+      <c r="V24" t="s">
+        <v>263</v>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25">
+        <v>88.751999999999995</v>
+      </c>
+      <c r="G25" s="2">
+        <v>46178.491689814808</v>
+      </c>
+      <c r="H25" t="s">
+        <v>161</v>
+      </c>
+      <c r="I25" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" t="s">
+        <v>161</v>
+      </c>
+      <c r="K25" t="s">
         <v>200</v>
       </c>
-      <c r="V24" t="s">
-        <v>188</v>
-      </c>
-      <c r="W24" t="s">
-        <v>263</v>
-      </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26">
-      <c r="A25" s="1">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" t="s">
-        <v>105</v>
-      </c>
-      <c r="F25" t="s">
-        <v>133</v>
-      </c>
-      <c r="G25">
-        <v>88.752</v>
-      </c>
-      <c r="H25" s="2">
-        <v>46178.49168981481</v>
-      </c>
-      <c r="I25" t="s">
-        <v>161</v>
-      </c>
-      <c r="J25" t="s">
-        <v>189</v>
-      </c>
-      <c r="K25" t="s">
-        <v>161</v>
-      </c>
       <c r="L25" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="M25" t="s">
         <v>226</v>
       </c>
       <c r="N25" t="s">
-        <v>226</v>
-      </c>
-      <c r="O25" t="s">
         <v>161</v>
       </c>
+      <c r="P25" t="s">
+        <v>233</v>
+      </c>
       <c r="Q25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="T25" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="U25" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="V25" t="s">
-        <v>189</v>
-      </c>
-      <c r="W25" t="s">
         <v>264</v>
       </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
       <c r="Y25" t="b">
         <v>0</v>
       </c>
-      <c r="Z25" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="26" spans="1:26">
-      <c r="A26" s="1">
-        <v>27</v>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26" t="s">
         <v>134</v>
       </c>
-      <c r="G26">
-        <v>1225.743</v>
-      </c>
-      <c r="H26" s="2">
-        <v>46178.49185185185</v>
+      <c r="F26">
+        <v>1225.7429999999999</v>
+      </c>
+      <c r="G26" s="2">
+        <v>46178.491851851853</v>
+      </c>
+      <c r="H26" t="s">
+        <v>162</v>
       </c>
       <c r="I26" t="s">
+        <v>190</v>
+      </c>
+      <c r="J26" t="s">
         <v>162</v>
       </c>
-      <c r="J26" t="s">
-        <v>190</v>
-      </c>
       <c r="K26" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="L26" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="M26" t="s">
         <v>227</v>
       </c>
       <c r="N26" t="s">
-        <v>227</v>
-      </c>
-      <c r="O26" t="s">
         <v>162</v>
       </c>
+      <c r="P26" t="s">
+        <v>233</v>
+      </c>
       <c r="Q26" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R26" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S26" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T26" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="U26" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="V26" t="s">
-        <v>190</v>
-      </c>
-      <c r="W26" t="s">
         <v>265</v>
       </c>
+      <c r="X26" t="b">
+        <v>0</v>
+      </c>
       <c r="Y26" t="b">
         <v>0</v>
       </c>
-      <c r="Z26" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="27" spans="1:26">
-      <c r="A27" s="1">
-        <v>28</v>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" t="s">
         <v>135</v>
       </c>
-      <c r="G27">
+      <c r="F27">
         <v>190.375</v>
       </c>
-      <c r="H27" s="2">
-        <v>46178.49197916667</v>
+      <c r="G27" s="2">
+        <v>46178.491979166669</v>
+      </c>
+      <c r="H27" t="s">
+        <v>163</v>
       </c>
       <c r="I27" t="s">
+        <v>191</v>
+      </c>
+      <c r="J27" t="s">
         <v>163</v>
       </c>
-      <c r="J27" t="s">
-        <v>191</v>
-      </c>
       <c r="K27" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="L27" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="M27" t="s">
         <v>228</v>
       </c>
       <c r="N27" t="s">
-        <v>228</v>
-      </c>
-      <c r="O27" t="s">
         <v>163</v>
       </c>
+      <c r="P27" t="s">
+        <v>233</v>
+      </c>
       <c r="Q27" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R27" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S27" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="T27" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="U27" t="s">
+        <v>191</v>
+      </c>
+      <c r="V27" t="s">
+        <v>266</v>
+      </c>
+      <c r="X27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28">
+        <v>21.960999999999999</v>
+      </c>
+      <c r="G28" s="2">
+        <v>46178.492002314822</v>
+      </c>
+      <c r="H28" t="s">
+        <v>164</v>
+      </c>
+      <c r="I28" t="s">
+        <v>192</v>
+      </c>
+      <c r="J28" t="s">
+        <v>164</v>
+      </c>
+      <c r="K28" t="s">
         <v>202</v>
       </c>
-      <c r="V27" t="s">
-        <v>191</v>
-      </c>
-      <c r="W27" t="s">
-        <v>266</v>
-      </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26">
-      <c r="A28" s="1">
-        <v>29</v>
-      </c>
-      <c r="B28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" t="s">
-        <v>136</v>
-      </c>
-      <c r="G28">
-        <v>21.961</v>
-      </c>
-      <c r="H28" s="2">
-        <v>46178.49200231482</v>
-      </c>
-      <c r="I28" t="s">
-        <v>164</v>
-      </c>
-      <c r="J28" t="s">
-        <v>192</v>
-      </c>
-      <c r="K28" t="s">
-        <v>164</v>
-      </c>
       <c r="L28" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="M28" t="s">
         <v>229</v>
       </c>
       <c r="N28" t="s">
-        <v>229</v>
-      </c>
-      <c r="O28" t="s">
         <v>164</v>
       </c>
+      <c r="P28" t="s">
+        <v>233</v>
+      </c>
       <c r="Q28" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R28" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S28" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="T28" t="s">
-        <v>240</v>
+        <v>202</v>
       </c>
       <c r="U28" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="V28" t="s">
-        <v>192</v>
-      </c>
-      <c r="W28" t="s">
         <v>267</v>
       </c>
+      <c r="X28" t="b">
+        <v>0</v>
+      </c>
       <c r="Y28" t="b">
         <v>0</v>
       </c>
-      <c r="Z28" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="29" spans="1:26">
-      <c r="A29" s="1">
-        <v>31</v>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
-        <v>109</v>
-      </c>
-      <c r="F29" t="s">
         <v>137</v>
       </c>
-      <c r="G29">
-        <v>138.719</v>
-      </c>
-      <c r="H29" s="2">
+      <c r="F29">
+        <v>138.71899999999999</v>
+      </c>
+      <c r="G29" s="2">
         <v>46178.4921412037</v>
       </c>
+      <c r="H29" t="s">
+        <v>165</v>
+      </c>
       <c r="I29" t="s">
+        <v>193</v>
+      </c>
+      <c r="J29" t="s">
         <v>165</v>
       </c>
-      <c r="J29" t="s">
-        <v>193</v>
-      </c>
       <c r="K29" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="L29" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="M29" t="s">
         <v>230</v>
       </c>
       <c r="N29" t="s">
-        <v>230</v>
-      </c>
-      <c r="O29" t="s">
         <v>165</v>
       </c>
+      <c r="P29" t="s">
+        <v>233</v>
+      </c>
       <c r="Q29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R29" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S29" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="T29" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="U29" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="V29" t="s">
-        <v>193</v>
-      </c>
-      <c r="W29" t="s">
         <v>268</v>
       </c>
+      <c r="X29" t="b">
+        <v>0</v>
+      </c>
       <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="b">
         <v>0</v>
       </c>
     </row>

--- a/excel/Salida.xlsx
+++ b/excel/Salida.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Developer\VacacionesOthman\GeoSupport\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EA2F1C-67F2-4038-BCDC-69CACCCDDBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="270">
   <si>
     <t>file_name</t>
   </si>
@@ -745,98 +739,101 @@
     <t>Puerto_Punta_Chungo_Drone</t>
   </si>
   <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_Drone\26_05_01\CL_MLP_PAO_IF_Ortho_26_05_01_estacion_cabeceras.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05_06\CL_MLP_PAO_IF_Ortho_26_05_06_eb3.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05_06\CL_MLP_PAO_IF_Ortho_26_05_06_ssee.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_06\CL_MLP_PAO_IF_Ortho_26_05_06_tramo_2_linea_33_kv_e_085_e_125.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_10\CL_MLP_PAO_IF_Ortho_26_05_10_ed1.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05_10\CL_MLP_PAO_IF_Ortho_26_05_10_helipuerto_mauro_mlp.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_10\CL_MLP_PAO_IF_Ortho_26_05_10_patio_19b.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_10\CL_MLP_PAO_IF_Ortho_26_05_10_em2.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_07\CL_MLP_PAO_IF_Ortho_26_05_07_tramo_2_linea_33_kv_e_048_e_084.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_10\CL_MLP_PAO_IF_Ortho_26_05_10_tramo_1_linea_33_kv_e_125_ml_eb2.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05_13\CL_MLP_PAO_IF_Ortho_26_05_13_estacion_de_monitoreo_n_2.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05_13\CL_MLP_PAO_IF_Ortho_26_05_13_acceso_pozos_prp.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_13\CL_MLP_PAO_IF_Ortho_26_05_13_subestacion_el_mauro.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_13\CL_MLP_PAO_IF_Ortho_26_05_13_em2_2.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05_13\CL_MLP_PAO_IF_Ortho_26_05_13_ebd.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_13\CL_MLP_PAO_IF_Ortho_26_05_13_ed2.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05_13\CL_MLP_PAO_IF_Ortho_26_05_13_estacion_de_bombeo_no3.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05_13\CL_MLP_PAO_IF_Ortho_26_05_13_pozos_prp.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_13\CL_MLP_PAO_IF_Ortho_26_05_13_estacion_intermedia_3.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_14\CL_MLP_PAO_IF_Ortho_26_05_14_em3.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05_14\CL_MLP_PAO_IF_Ortho_26_05_14_camino_alternativo_salamanca.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05_14\CL_MLP_PAO_IF_Ortho_26_05_14_em4.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_15\CL_MLP_PAO_IF_Ortho_26_05_15_ev1.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_Drone\26_05_15\CL_MLP_PAO_IF_Ortho_26_05_15_estacion_cabecera.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05_16\CL_MLP_PAO_IF_Ortho_26_05_16_torres_e48_a_e84.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Puerto_Punta_Chungo_Drone\26_05_17\CL_MLP_PAO_IF_Ortho_26_05_17_ev2.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Puerto_Punta_Chungo_Drone\26_05_17\CL_MLP_PAO_IF_Ortho_26_05_17_edt.tif</t>
-  </si>
-  <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_Drone\26_05_15\CL_MLP_PAO_IF_Ortho_26_05_15_em1.tif</t>
+    <t>26_05</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_01_estacion_cabeceras.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_06_eb3.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_06_ssee.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_06_tramo_2_linea_33_kv_e_085_e_125.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_10_ed1.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_10_helipuerto_mauro_mlp.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_10_patio_19b.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_10_em2.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_07_tramo_2_linea_33_kv_e_048_e_084.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_10_tramo_1_linea_33_kv_e_125_ml_eb2.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_13_estacion_de_monitoreo_n_2.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_13_acceso_pozos_prp.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_13_subestacion_el_mauro.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_13_em2_2.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_13_ebd.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_13_ed2.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_13_estacion_de_bombeo_no3.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_13_pozos_prp.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_13_estacion_intermedia_3.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_14_em3.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_14_camino_alternativo_salamanca.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_14_em4.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_15_ev1.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_15_estacion_cabecera.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_16_torres_e48_a_e84.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Puerto_Punta_Chungo_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_17_ev2.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Puerto_Punta_Chungo_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_17_edt.tif</t>
+  </si>
+  <si>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_15_em1.tif</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -900,21 +897,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -952,7 +941,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -986,7 +975,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1021,10 +1009,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1197,2099 +1184,2156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="82" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="186.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="62.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="64.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="62.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="32.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="34" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="94" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="34.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="64.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="132.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.44140625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="1:26">
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:26">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>81</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>82</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>110</v>
       </c>
-      <c r="F2">
-        <v>79.159000000000006</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="G2">
+        <v>79.15900000000001</v>
+      </c>
+      <c r="H2" s="2">
         <v>46178.48945601852</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>138</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>166</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>138</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>194</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>203</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>231</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>232</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>233</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>234</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>235</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>236</v>
       </c>
-      <c r="T2" t="s">
-        <v>194</v>
-      </c>
       <c r="U2" t="s">
+        <v>241</v>
+      </c>
+      <c r="V2" t="s">
         <v>166</v>
       </c>
-      <c r="V2" t="s">
-        <v>241</v>
-      </c>
-      <c r="X2" t="b">
-        <v>0</v>
+      <c r="W2" t="s">
+        <v>242</v>
       </c>
       <c r="Y2" t="b">
         <v>0</v>
       </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:26">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>54</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>81</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>83</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>111</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>11.012</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>46178.48946759259</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>139</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>167</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>139</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>195</v>
-      </c>
-      <c r="L3" t="s">
-        <v>204</v>
       </c>
       <c r="M3" t="s">
         <v>204</v>
       </c>
       <c r="N3" t="s">
+        <v>204</v>
+      </c>
+      <c r="O3" t="s">
         <v>139</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>233</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>234</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>235</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>237</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
+        <v>241</v>
+      </c>
+      <c r="V3" t="s">
+        <v>167</v>
+      </c>
+      <c r="W3" t="s">
+        <v>243</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4">
+        <v>762.001</v>
+      </c>
+      <c r="H4" s="2">
+        <v>46178.48954861111</v>
+      </c>
+      <c r="I4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" t="s">
+        <v>168</v>
+      </c>
+      <c r="K4" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" t="s">
         <v>195</v>
-      </c>
-      <c r="U3" t="s">
-        <v>167</v>
-      </c>
-      <c r="V3" t="s">
-        <v>242</v>
-      </c>
-      <c r="X3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F4">
-        <v>762.00099999999998</v>
-      </c>
-      <c r="G4" s="2">
-        <v>46178.489548611113</v>
-      </c>
-      <c r="H4" t="s">
-        <v>140</v>
-      </c>
-      <c r="I4" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K4" t="s">
-        <v>195</v>
-      </c>
-      <c r="L4" t="s">
-        <v>205</v>
       </c>
       <c r="M4" t="s">
         <v>205</v>
       </c>
       <c r="N4" t="s">
+        <v>205</v>
+      </c>
+      <c r="O4" t="s">
         <v>140</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>233</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>234</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>235</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>237</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
+        <v>241</v>
+      </c>
+      <c r="V4" t="s">
+        <v>168</v>
+      </c>
+      <c r="W4" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5">
+        <v>640.965</v>
+      </c>
+      <c r="H5" s="2">
+        <v>46178.48971064815</v>
+      </c>
+      <c r="I5" t="s">
+        <v>141</v>
+      </c>
+      <c r="J5" t="s">
+        <v>169</v>
+      </c>
+      <c r="K5" t="s">
+        <v>141</v>
+      </c>
+      <c r="L5" t="s">
         <v>195</v>
-      </c>
-      <c r="U4" t="s">
-        <v>168</v>
-      </c>
-      <c r="V4" t="s">
-        <v>243</v>
-      </c>
-      <c r="X4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5">
-        <v>640.96500000000003</v>
-      </c>
-      <c r="G5" s="2">
-        <v>46178.489710648151</v>
-      </c>
-      <c r="H5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I5" t="s">
-        <v>169</v>
-      </c>
-      <c r="J5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K5" t="s">
-        <v>195</v>
-      </c>
-      <c r="L5" t="s">
-        <v>206</v>
       </c>
       <c r="M5" t="s">
         <v>206</v>
       </c>
       <c r="N5" t="s">
+        <v>206</v>
+      </c>
+      <c r="O5" t="s">
         <v>141</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>233</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>234</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>235</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>238</v>
       </c>
-      <c r="T5" t="s">
-        <v>195</v>
-      </c>
       <c r="U5" t="s">
+        <v>241</v>
+      </c>
+      <c r="V5" t="s">
         <v>169</v>
       </c>
-      <c r="V5" t="s">
-        <v>244</v>
-      </c>
-      <c r="X5" t="b">
-        <v>0</v>
+      <c r="W5" t="s">
+        <v>245</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
       </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:26">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>57</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>81</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>86</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>114</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>63.628</v>
       </c>
-      <c r="G6" s="2">
-        <v>46178.489791666667</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2">
+        <v>46178.48979166667</v>
+      </c>
+      <c r="I6" t="s">
         <v>142</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>170</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>142</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>196</v>
-      </c>
-      <c r="L6" t="s">
-        <v>207</v>
       </c>
       <c r="M6" t="s">
         <v>207</v>
       </c>
       <c r="N6" t="s">
+        <v>207</v>
+      </c>
+      <c r="O6" t="s">
         <v>142</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>233</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>234</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>235</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>238</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
+        <v>241</v>
+      </c>
+      <c r="V6" t="s">
+        <v>170</v>
+      </c>
+      <c r="W6" t="s">
+        <v>246</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" t="s">
+        <v>115</v>
+      </c>
+      <c r="G7">
+        <v>102.047</v>
+      </c>
+      <c r="H7" s="2">
+        <v>46178.48983796296</v>
+      </c>
+      <c r="I7" t="s">
+        <v>143</v>
+      </c>
+      <c r="J7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K7" t="s">
+        <v>143</v>
+      </c>
+      <c r="L7" t="s">
         <v>196</v>
-      </c>
-      <c r="U6" t="s">
-        <v>170</v>
-      </c>
-      <c r="V6" t="s">
-        <v>245</v>
-      </c>
-      <c r="X6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7">
-        <v>102.047</v>
-      </c>
-      <c r="G7" s="2">
-        <v>46178.489837962959</v>
-      </c>
-      <c r="H7" t="s">
-        <v>143</v>
-      </c>
-      <c r="I7" t="s">
-        <v>171</v>
-      </c>
-      <c r="J7" t="s">
-        <v>143</v>
-      </c>
-      <c r="K7" t="s">
-        <v>196</v>
-      </c>
-      <c r="L7" t="s">
-        <v>208</v>
       </c>
       <c r="M7" t="s">
         <v>208</v>
       </c>
       <c r="N7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O7" t="s">
         <v>143</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>233</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>234</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>235</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>237</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
+        <v>241</v>
+      </c>
+      <c r="V7" t="s">
+        <v>171</v>
+      </c>
+      <c r="W7" t="s">
+        <v>247</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8">
+        <v>156.844</v>
+      </c>
+      <c r="H8" s="2">
+        <v>46178.48986111111</v>
+      </c>
+      <c r="I8" t="s">
+        <v>144</v>
+      </c>
+      <c r="J8" t="s">
+        <v>172</v>
+      </c>
+      <c r="K8" t="s">
+        <v>144</v>
+      </c>
+      <c r="L8" t="s">
         <v>196</v>
-      </c>
-      <c r="U7" t="s">
-        <v>171</v>
-      </c>
-      <c r="V7" t="s">
-        <v>246</v>
-      </c>
-      <c r="X7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8">
-        <v>156.84399999999999</v>
-      </c>
-      <c r="G8" s="2">
-        <v>46178.489861111113</v>
-      </c>
-      <c r="H8" t="s">
-        <v>144</v>
-      </c>
-      <c r="I8" t="s">
-        <v>172</v>
-      </c>
-      <c r="J8" t="s">
-        <v>144</v>
-      </c>
-      <c r="K8" t="s">
-        <v>196</v>
-      </c>
-      <c r="L8" t="s">
-        <v>209</v>
       </c>
       <c r="M8" t="s">
         <v>209</v>
       </c>
       <c r="N8" t="s">
+        <v>209</v>
+      </c>
+      <c r="O8" t="s">
         <v>144</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>233</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>234</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>235</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>238</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
+        <v>241</v>
+      </c>
+      <c r="V8" t="s">
+        <v>172</v>
+      </c>
+      <c r="W8" t="s">
+        <v>248</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9">
+        <v>71.19</v>
+      </c>
+      <c r="H9" s="2">
+        <v>46178.48991898148</v>
+      </c>
+      <c r="I9" t="s">
+        <v>145</v>
+      </c>
+      <c r="J9" t="s">
+        <v>173</v>
+      </c>
+      <c r="K9" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" t="s">
         <v>196</v>
-      </c>
-      <c r="U8" t="s">
-        <v>172</v>
-      </c>
-      <c r="V8" t="s">
-        <v>247</v>
-      </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" t="s">
-        <v>117</v>
-      </c>
-      <c r="F9">
-        <v>71.19</v>
-      </c>
-      <c r="G9" s="2">
-        <v>46178.489918981482</v>
-      </c>
-      <c r="H9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I9" t="s">
-        <v>173</v>
-      </c>
-      <c r="J9" t="s">
-        <v>145</v>
-      </c>
-      <c r="K9" t="s">
-        <v>196</v>
-      </c>
-      <c r="L9" t="s">
-        <v>210</v>
       </c>
       <c r="M9" t="s">
         <v>210</v>
       </c>
       <c r="N9" t="s">
+        <v>210</v>
+      </c>
+      <c r="O9" t="s">
         <v>145</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>233</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>234</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>235</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>238</v>
       </c>
-      <c r="T9" t="s">
-        <v>196</v>
-      </c>
       <c r="U9" t="s">
+        <v>241</v>
+      </c>
+      <c r="V9" t="s">
         <v>173</v>
       </c>
-      <c r="V9" t="s">
-        <v>248</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
+      <c r="W9" t="s">
+        <v>249</v>
       </c>
       <c r="Y9" t="b">
         <v>0</v>
       </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:26">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>61</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>81</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>90</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>118</v>
       </c>
-      <c r="F10">
-        <v>3217.5630000000001</v>
-      </c>
-      <c r="G10" s="2">
-        <v>46178.490266203713</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="G10">
+        <v>3217.563</v>
+      </c>
+      <c r="H10" s="2">
+        <v>46178.49026620371</v>
+      </c>
+      <c r="I10" t="s">
         <v>146</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>174</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>146</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>197</v>
-      </c>
-      <c r="L10" t="s">
-        <v>211</v>
       </c>
       <c r="M10" t="s">
         <v>211</v>
       </c>
       <c r="N10" t="s">
+        <v>211</v>
+      </c>
+      <c r="O10" t="s">
         <v>146</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>233</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>234</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>235</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>238</v>
       </c>
-      <c r="T10" t="s">
-        <v>197</v>
-      </c>
       <c r="U10" t="s">
+        <v>241</v>
+      </c>
+      <c r="V10" t="s">
         <v>174</v>
       </c>
-      <c r="V10" t="s">
-        <v>249</v>
-      </c>
-      <c r="X10" t="b">
-        <v>0</v>
+      <c r="W10" t="s">
+        <v>250</v>
       </c>
       <c r="Y10" t="b">
         <v>0</v>
       </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:26">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>62</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>81</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>91</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>119</v>
       </c>
-      <c r="F11">
-        <v>264.28199999999998</v>
-      </c>
-      <c r="G11" s="2">
-        <v>46178.490358796298</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="G11">
+        <v>264.282</v>
+      </c>
+      <c r="H11" s="2">
+        <v>46178.4903587963</v>
+      </c>
+      <c r="I11" t="s">
         <v>147</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>175</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>147</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>196</v>
-      </c>
-      <c r="L11" t="s">
-        <v>212</v>
       </c>
       <c r="M11" t="s">
         <v>212</v>
       </c>
       <c r="N11" t="s">
+        <v>212</v>
+      </c>
+      <c r="O11" t="s">
         <v>147</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>233</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>234</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>235</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
         <v>238</v>
       </c>
-      <c r="T11" t="s">
-        <v>196</v>
-      </c>
       <c r="U11" t="s">
+        <v>241</v>
+      </c>
+      <c r="V11" t="s">
         <v>175</v>
       </c>
-      <c r="V11" t="s">
-        <v>250</v>
-      </c>
-      <c r="X11" t="b">
-        <v>0</v>
+      <c r="W11" t="s">
+        <v>251</v>
       </c>
       <c r="Y11" t="b">
         <v>0</v>
       </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:26">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>63</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>92</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>120</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>531.553</v>
       </c>
-      <c r="G12" s="2">
-        <v>46178.490451388891</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="H12" s="2">
+        <v>46178.49045138889</v>
+      </c>
+      <c r="I12" t="s">
         <v>148</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>176</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>148</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>198</v>
-      </c>
-      <c r="L12" t="s">
-        <v>213</v>
       </c>
       <c r="M12" t="s">
         <v>213</v>
       </c>
       <c r="N12" t="s">
+        <v>213</v>
+      </c>
+      <c r="O12" t="s">
         <v>148</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>233</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>234</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>235</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>237</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
+        <v>241</v>
+      </c>
+      <c r="V12" t="s">
+        <v>176</v>
+      </c>
+      <c r="W12" t="s">
+        <v>252</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13">
+        <v>399.55</v>
+      </c>
+      <c r="H13" s="2">
+        <v>46178.49055555555</v>
+      </c>
+      <c r="I13" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" t="s">
+        <v>177</v>
+      </c>
+      <c r="K13" t="s">
+        <v>149</v>
+      </c>
+      <c r="L13" t="s">
         <v>198</v>
-      </c>
-      <c r="U12" t="s">
-        <v>176</v>
-      </c>
-      <c r="V12" t="s">
-        <v>251</v>
-      </c>
-      <c r="X12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F13">
-        <v>399.55</v>
-      </c>
-      <c r="G13" s="2">
-        <v>46178.490555555552</v>
-      </c>
-      <c r="H13" t="s">
-        <v>149</v>
-      </c>
-      <c r="I13" t="s">
-        <v>177</v>
-      </c>
-      <c r="J13" t="s">
-        <v>149</v>
-      </c>
-      <c r="K13" t="s">
-        <v>198</v>
-      </c>
-      <c r="L13" t="s">
-        <v>214</v>
       </c>
       <c r="M13" t="s">
         <v>214</v>
       </c>
       <c r="N13" t="s">
+        <v>214</v>
+      </c>
+      <c r="O13" t="s">
         <v>149</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>233</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>234</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>235</v>
       </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
         <v>237</v>
       </c>
-      <c r="T13" t="s">
+      <c r="U13" t="s">
+        <v>241</v>
+      </c>
+      <c r="V13" t="s">
+        <v>177</v>
+      </c>
+      <c r="W13" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14">
+        <v>954.304</v>
+      </c>
+      <c r="H14" s="2">
+        <v>46178.49065972222</v>
+      </c>
+      <c r="I14" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" t="s">
+        <v>178</v>
+      </c>
+      <c r="K14" t="s">
+        <v>150</v>
+      </c>
+      <c r="L14" t="s">
         <v>198</v>
-      </c>
-      <c r="U13" t="s">
-        <v>177</v>
-      </c>
-      <c r="V13" t="s">
-        <v>252</v>
-      </c>
-      <c r="X13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" t="s">
-        <v>122</v>
-      </c>
-      <c r="F14">
-        <v>954.30399999999997</v>
-      </c>
-      <c r="G14" s="2">
-        <v>46178.490659722222</v>
-      </c>
-      <c r="H14" t="s">
-        <v>150</v>
-      </c>
-      <c r="I14" t="s">
-        <v>178</v>
-      </c>
-      <c r="J14" t="s">
-        <v>150</v>
-      </c>
-      <c r="K14" t="s">
-        <v>198</v>
-      </c>
-      <c r="L14" t="s">
-        <v>215</v>
       </c>
       <c r="M14" t="s">
         <v>215</v>
       </c>
       <c r="N14" t="s">
+        <v>215</v>
+      </c>
+      <c r="O14" t="s">
         <v>150</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>233</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>234</v>
       </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>235</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>238</v>
       </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
+        <v>241</v>
+      </c>
+      <c r="V14" t="s">
+        <v>178</v>
+      </c>
+      <c r="W14" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15">
+        <v>156.937</v>
+      </c>
+      <c r="H15" s="2">
+        <v>46178.49068287037</v>
+      </c>
+      <c r="I15" t="s">
+        <v>151</v>
+      </c>
+      <c r="J15" t="s">
+        <v>179</v>
+      </c>
+      <c r="K15" t="s">
+        <v>151</v>
+      </c>
+      <c r="L15" t="s">
         <v>198</v>
-      </c>
-      <c r="U14" t="s">
-        <v>178</v>
-      </c>
-      <c r="V14" t="s">
-        <v>253</v>
-      </c>
-      <c r="X14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15">
-        <v>156.93700000000001</v>
-      </c>
-      <c r="G15" s="2">
-        <v>46178.490682870368</v>
-      </c>
-      <c r="H15" t="s">
-        <v>151</v>
-      </c>
-      <c r="I15" t="s">
-        <v>179</v>
-      </c>
-      <c r="J15" t="s">
-        <v>151</v>
-      </c>
-      <c r="K15" t="s">
-        <v>198</v>
-      </c>
-      <c r="L15" t="s">
-        <v>216</v>
       </c>
       <c r="M15" t="s">
         <v>216</v>
       </c>
       <c r="N15" t="s">
+        <v>216</v>
+      </c>
+      <c r="O15" t="s">
         <v>151</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>233</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>234</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>235</v>
       </c>
-      <c r="S15" t="s">
+      <c r="T15" t="s">
         <v>238</v>
       </c>
-      <c r="T15" t="s">
+      <c r="U15" t="s">
+        <v>241</v>
+      </c>
+      <c r="V15" t="s">
+        <v>179</v>
+      </c>
+      <c r="W15" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" t="s">
+        <v>124</v>
+      </c>
+      <c r="G16">
+        <v>213.754</v>
+      </c>
+      <c r="H16" s="2">
+        <v>46178.49072916667</v>
+      </c>
+      <c r="I16" t="s">
+        <v>152</v>
+      </c>
+      <c r="J16" t="s">
+        <v>180</v>
+      </c>
+      <c r="K16" t="s">
+        <v>152</v>
+      </c>
+      <c r="L16" t="s">
         <v>198</v>
-      </c>
-      <c r="U15" t="s">
-        <v>179</v>
-      </c>
-      <c r="V15" t="s">
-        <v>254</v>
-      </c>
-      <c r="X15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16">
-        <v>213.75399999999999</v>
-      </c>
-      <c r="G16" s="2">
-        <v>46178.490729166668</v>
-      </c>
-      <c r="H16" t="s">
-        <v>152</v>
-      </c>
-      <c r="I16" t="s">
-        <v>180</v>
-      </c>
-      <c r="J16" t="s">
-        <v>152</v>
-      </c>
-      <c r="K16" t="s">
-        <v>198</v>
-      </c>
-      <c r="L16" t="s">
-        <v>217</v>
       </c>
       <c r="M16" t="s">
         <v>217</v>
       </c>
       <c r="N16" t="s">
+        <v>217</v>
+      </c>
+      <c r="O16" t="s">
         <v>152</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>233</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>234</v>
       </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
         <v>235</v>
       </c>
-      <c r="S16" t="s">
+      <c r="T16" t="s">
         <v>237</v>
       </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
+        <v>241</v>
+      </c>
+      <c r="V16" t="s">
+        <v>180</v>
+      </c>
+      <c r="W16" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17">
+        <v>820.8339999999999</v>
+      </c>
+      <c r="H17" s="2">
+        <v>46178.49083333334</v>
+      </c>
+      <c r="I17" t="s">
+        <v>153</v>
+      </c>
+      <c r="J17" t="s">
+        <v>181</v>
+      </c>
+      <c r="K17" t="s">
+        <v>153</v>
+      </c>
+      <c r="L17" t="s">
         <v>198</v>
-      </c>
-      <c r="U16" t="s">
-        <v>180</v>
-      </c>
-      <c r="V16" t="s">
-        <v>255</v>
-      </c>
-      <c r="X16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" t="s">
-        <v>125</v>
-      </c>
-      <c r="F17">
-        <v>820.83399999999995</v>
-      </c>
-      <c r="G17" s="2">
-        <v>46178.490833333337</v>
-      </c>
-      <c r="H17" t="s">
-        <v>153</v>
-      </c>
-      <c r="I17" t="s">
-        <v>181</v>
-      </c>
-      <c r="J17" t="s">
-        <v>153</v>
-      </c>
-      <c r="K17" t="s">
-        <v>198</v>
-      </c>
-      <c r="L17" t="s">
-        <v>218</v>
       </c>
       <c r="M17" t="s">
         <v>218</v>
       </c>
       <c r="N17" t="s">
+        <v>218</v>
+      </c>
+      <c r="O17" t="s">
         <v>153</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>233</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>234</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>235</v>
       </c>
-      <c r="S17" t="s">
+      <c r="T17" t="s">
         <v>238</v>
       </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
+        <v>241</v>
+      </c>
+      <c r="V17" t="s">
+        <v>181</v>
+      </c>
+      <c r="W17" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18">
+        <v>56.175</v>
+      </c>
+      <c r="H18" s="2">
+        <v>46178.49086805555</v>
+      </c>
+      <c r="I18" t="s">
+        <v>154</v>
+      </c>
+      <c r="J18" t="s">
+        <v>182</v>
+      </c>
+      <c r="K18" t="s">
+        <v>154</v>
+      </c>
+      <c r="L18" t="s">
         <v>198</v>
-      </c>
-      <c r="U17" t="s">
-        <v>181</v>
-      </c>
-      <c r="V17" t="s">
-        <v>256</v>
-      </c>
-      <c r="X17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" t="s">
-        <v>126</v>
-      </c>
-      <c r="F18">
-        <v>56.174999999999997</v>
-      </c>
-      <c r="G18" s="2">
-        <v>46178.490868055553</v>
-      </c>
-      <c r="H18" t="s">
-        <v>154</v>
-      </c>
-      <c r="I18" t="s">
-        <v>182</v>
-      </c>
-      <c r="J18" t="s">
-        <v>154</v>
-      </c>
-      <c r="K18" t="s">
-        <v>198</v>
-      </c>
-      <c r="L18" t="s">
-        <v>219</v>
       </c>
       <c r="M18" t="s">
         <v>219</v>
       </c>
       <c r="N18" t="s">
+        <v>219</v>
+      </c>
+      <c r="O18" t="s">
         <v>154</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>233</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>234</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>235</v>
       </c>
-      <c r="S18" t="s">
+      <c r="T18" t="s">
         <v>237</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
+        <v>241</v>
+      </c>
+      <c r="V18" t="s">
+        <v>182</v>
+      </c>
+      <c r="W18" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19">
+        <v>29.052</v>
+      </c>
+      <c r="H19" s="2">
+        <v>46178.49089120371</v>
+      </c>
+      <c r="I19" t="s">
+        <v>155</v>
+      </c>
+      <c r="J19" t="s">
+        <v>183</v>
+      </c>
+      <c r="K19" t="s">
+        <v>155</v>
+      </c>
+      <c r="L19" t="s">
         <v>198</v>
-      </c>
-      <c r="U18" t="s">
-        <v>182</v>
-      </c>
-      <c r="V18" t="s">
-        <v>257</v>
-      </c>
-      <c r="X18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" t="s">
-        <v>127</v>
-      </c>
-      <c r="F19">
-        <v>29.052</v>
-      </c>
-      <c r="G19" s="2">
-        <v>46178.490891203714</v>
-      </c>
-      <c r="H19" t="s">
-        <v>155</v>
-      </c>
-      <c r="I19" t="s">
-        <v>183</v>
-      </c>
-      <c r="J19" t="s">
-        <v>155</v>
-      </c>
-      <c r="K19" t="s">
-        <v>198</v>
-      </c>
-      <c r="L19" t="s">
-        <v>220</v>
       </c>
       <c r="M19" t="s">
         <v>220</v>
       </c>
       <c r="N19" t="s">
+        <v>220</v>
+      </c>
+      <c r="O19" t="s">
         <v>155</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>233</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>234</v>
       </c>
-      <c r="R19" t="s">
+      <c r="S19" t="s">
         <v>235</v>
       </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
         <v>237</v>
       </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
+        <v>241</v>
+      </c>
+      <c r="V19" t="s">
+        <v>183</v>
+      </c>
+      <c r="W19" t="s">
+        <v>259</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20">
+        <v>1813.409</v>
+      </c>
+      <c r="H20" s="2">
+        <v>46178.49106481481</v>
+      </c>
+      <c r="I20" t="s">
+        <v>156</v>
+      </c>
+      <c r="J20" t="s">
+        <v>184</v>
+      </c>
+      <c r="K20" t="s">
+        <v>156</v>
+      </c>
+      <c r="L20" t="s">
         <v>198</v>
-      </c>
-      <c r="U19" t="s">
-        <v>183</v>
-      </c>
-      <c r="V19" t="s">
-        <v>258</v>
-      </c>
-      <c r="X19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20">
-        <v>1813.4090000000001</v>
-      </c>
-      <c r="G20" s="2">
-        <v>46178.491064814807</v>
-      </c>
-      <c r="H20" t="s">
-        <v>156</v>
-      </c>
-      <c r="I20" t="s">
-        <v>184</v>
-      </c>
-      <c r="J20" t="s">
-        <v>156</v>
-      </c>
-      <c r="K20" t="s">
-        <v>198</v>
-      </c>
-      <c r="L20" t="s">
-        <v>221</v>
       </c>
       <c r="M20" t="s">
         <v>221</v>
       </c>
       <c r="N20" t="s">
+        <v>221</v>
+      </c>
+      <c r="O20" t="s">
         <v>156</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>233</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>234</v>
       </c>
-      <c r="R20" t="s">
+      <c r="S20" t="s">
         <v>235</v>
       </c>
-      <c r="S20" t="s">
+      <c r="T20" t="s">
         <v>238</v>
       </c>
-      <c r="T20" t="s">
-        <v>198</v>
-      </c>
       <c r="U20" t="s">
+        <v>241</v>
+      </c>
+      <c r="V20" t="s">
         <v>184</v>
       </c>
-      <c r="V20" t="s">
-        <v>259</v>
-      </c>
-      <c r="X20" t="b">
-        <v>0</v>
+      <c r="W20" t="s">
+        <v>260</v>
       </c>
       <c r="Y20" t="b">
         <v>0</v>
       </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:26">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>72</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>81</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>101</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>129</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>1021.143</v>
       </c>
-      <c r="G21" s="2">
+      <c r="H21" s="2">
         <v>46178.49119212963</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>157</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>185</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>157</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>199</v>
-      </c>
-      <c r="L21" t="s">
-        <v>222</v>
       </c>
       <c r="M21" t="s">
         <v>222</v>
       </c>
       <c r="N21" t="s">
+        <v>222</v>
+      </c>
+      <c r="O21" t="s">
         <v>157</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>233</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>234</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>235</v>
       </c>
-      <c r="S21" t="s">
+      <c r="T21" t="s">
         <v>238</v>
       </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
+        <v>241</v>
+      </c>
+      <c r="V21" t="s">
+        <v>185</v>
+      </c>
+      <c r="W21" t="s">
+        <v>261</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" t="s">
+        <v>130</v>
+      </c>
+      <c r="G22">
+        <v>56.639</v>
+      </c>
+      <c r="H22" s="2">
+        <v>46178.49123842592</v>
+      </c>
+      <c r="I22" t="s">
+        <v>158</v>
+      </c>
+      <c r="J22" t="s">
+        <v>186</v>
+      </c>
+      <c r="K22" t="s">
+        <v>158</v>
+      </c>
+      <c r="L22" t="s">
         <v>199</v>
-      </c>
-      <c r="U21" t="s">
-        <v>185</v>
-      </c>
-      <c r="V21" t="s">
-        <v>260</v>
-      </c>
-      <c r="X21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" t="s">
-        <v>130</v>
-      </c>
-      <c r="F22">
-        <v>56.639000000000003</v>
-      </c>
-      <c r="G22" s="2">
-        <v>46178.491238425922</v>
-      </c>
-      <c r="H22" t="s">
-        <v>158</v>
-      </c>
-      <c r="I22" t="s">
-        <v>186</v>
-      </c>
-      <c r="J22" t="s">
-        <v>158</v>
-      </c>
-      <c r="K22" t="s">
-        <v>199</v>
-      </c>
-      <c r="L22" t="s">
-        <v>223</v>
       </c>
       <c r="M22" t="s">
         <v>223</v>
       </c>
       <c r="N22" t="s">
+        <v>223</v>
+      </c>
+      <c r="O22" t="s">
         <v>158</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>233</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>234</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
         <v>235</v>
       </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>237</v>
       </c>
-      <c r="T22" t="s">
+      <c r="U22" t="s">
+        <v>241</v>
+      </c>
+      <c r="V22" t="s">
+        <v>186</v>
+      </c>
+      <c r="W22" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23">
+        <v>2073.665</v>
+      </c>
+      <c r="H23" s="2">
+        <v>46178.49150462963</v>
+      </c>
+      <c r="I23" t="s">
+        <v>159</v>
+      </c>
+      <c r="J23" t="s">
+        <v>187</v>
+      </c>
+      <c r="K23" t="s">
+        <v>159</v>
+      </c>
+      <c r="L23" t="s">
         <v>199</v>
-      </c>
-      <c r="U22" t="s">
-        <v>186</v>
-      </c>
-      <c r="V22" t="s">
-        <v>261</v>
-      </c>
-      <c r="X22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23">
-        <v>2073.665</v>
-      </c>
-      <c r="G23" s="2">
-        <v>46178.49150462963</v>
-      </c>
-      <c r="H23" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" t="s">
-        <v>187</v>
-      </c>
-      <c r="J23" t="s">
-        <v>159</v>
-      </c>
-      <c r="K23" t="s">
-        <v>199</v>
-      </c>
-      <c r="L23" t="s">
-        <v>224</v>
       </c>
       <c r="M23" t="s">
         <v>224</v>
       </c>
       <c r="N23" t="s">
+        <v>224</v>
+      </c>
+      <c r="O23" t="s">
         <v>159</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>233</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>234</v>
       </c>
-      <c r="R23" t="s">
+      <c r="S23" t="s">
         <v>235</v>
       </c>
-      <c r="S23" t="s">
+      <c r="T23" t="s">
         <v>237</v>
       </c>
-      <c r="T23" t="s">
-        <v>199</v>
-      </c>
       <c r="U23" t="s">
+        <v>241</v>
+      </c>
+      <c r="V23" t="s">
         <v>187</v>
       </c>
-      <c r="V23" t="s">
-        <v>262</v>
-      </c>
-      <c r="X23" t="b">
-        <v>0</v>
+      <c r="W23" t="s">
+        <v>263</v>
       </c>
       <c r="Y23" t="b">
         <v>0</v>
       </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="24" spans="1:26">
+      <c r="A24" s="1">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
         <v>47</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>75</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>81</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>104</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>132</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>721.83</v>
       </c>
-      <c r="G24" s="2">
-        <v>46178.491655092592</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="H24" s="2">
+        <v>46178.49165509259</v>
+      </c>
+      <c r="I24" t="s">
         <v>160</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>188</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>160</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>200</v>
-      </c>
-      <c r="L24" t="s">
-        <v>225</v>
       </c>
       <c r="M24" t="s">
         <v>225</v>
       </c>
       <c r="N24" t="s">
+        <v>225</v>
+      </c>
+      <c r="O24" t="s">
         <v>160</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>233</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>234</v>
       </c>
-      <c r="R24" t="s">
+      <c r="S24" t="s">
         <v>235</v>
       </c>
-      <c r="S24" t="s">
+      <c r="T24" t="s">
         <v>238</v>
       </c>
-      <c r="T24" t="s">
+      <c r="U24" t="s">
+        <v>241</v>
+      </c>
+      <c r="V24" t="s">
+        <v>188</v>
+      </c>
+      <c r="W24" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26">
+      <c r="A25" s="1">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25">
+        <v>88.752</v>
+      </c>
+      <c r="H25" s="2">
+        <v>46178.49168981481</v>
+      </c>
+      <c r="I25" t="s">
+        <v>161</v>
+      </c>
+      <c r="J25" t="s">
+        <v>189</v>
+      </c>
+      <c r="K25" t="s">
+        <v>161</v>
+      </c>
+      <c r="L25" t="s">
         <v>200</v>
-      </c>
-      <c r="U24" t="s">
-        <v>188</v>
-      </c>
-      <c r="V24" t="s">
-        <v>263</v>
-      </c>
-      <c r="X24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" t="s">
-        <v>133</v>
-      </c>
-      <c r="F25">
-        <v>88.751999999999995</v>
-      </c>
-      <c r="G25" s="2">
-        <v>46178.491689814808</v>
-      </c>
-      <c r="H25" t="s">
-        <v>161</v>
-      </c>
-      <c r="I25" t="s">
-        <v>189</v>
-      </c>
-      <c r="J25" t="s">
-        <v>161</v>
-      </c>
-      <c r="K25" t="s">
-        <v>200</v>
-      </c>
-      <c r="L25" t="s">
-        <v>226</v>
       </c>
       <c r="M25" t="s">
         <v>226</v>
       </c>
       <c r="N25" t="s">
+        <v>226</v>
+      </c>
+      <c r="O25" t="s">
         <v>161</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>233</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>234</v>
       </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>235</v>
       </c>
-      <c r="S25" t="s">
+      <c r="T25" t="s">
         <v>236</v>
       </c>
-      <c r="T25" t="s">
-        <v>200</v>
-      </c>
       <c r="U25" t="s">
+        <v>241</v>
+      </c>
+      <c r="V25" t="s">
         <v>189</v>
       </c>
-      <c r="V25" t="s">
-        <v>264</v>
-      </c>
-      <c r="X25" t="b">
-        <v>0</v>
+      <c r="W25" t="s">
+        <v>265</v>
       </c>
       <c r="Y25" t="b">
         <v>0</v>
       </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="26" spans="1:26">
+      <c r="A26" s="1">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
         <v>49</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>77</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>81</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>106</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>134</v>
       </c>
-      <c r="F26">
-        <v>1225.7429999999999</v>
-      </c>
-      <c r="G26" s="2">
-        <v>46178.491851851853</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="G26">
+        <v>1225.743</v>
+      </c>
+      <c r="H26" s="2">
+        <v>46178.49185185185</v>
+      </c>
+      <c r="I26" t="s">
         <v>162</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>190</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>162</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>201</v>
-      </c>
-      <c r="L26" t="s">
-        <v>227</v>
       </c>
       <c r="M26" t="s">
         <v>227</v>
       </c>
       <c r="N26" t="s">
+        <v>227</v>
+      </c>
+      <c r="O26" t="s">
         <v>162</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>233</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>234</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26" t="s">
         <v>235</v>
       </c>
-      <c r="S26" t="s">
+      <c r="T26" t="s">
         <v>238</v>
       </c>
-      <c r="T26" t="s">
-        <v>201</v>
-      </c>
       <c r="U26" t="s">
+        <v>241</v>
+      </c>
+      <c r="V26" t="s">
         <v>190</v>
       </c>
-      <c r="V26" t="s">
-        <v>265</v>
-      </c>
-      <c r="X26" t="b">
-        <v>0</v>
+      <c r="W26" t="s">
+        <v>266</v>
       </c>
       <c r="Y26" t="b">
         <v>0</v>
       </c>
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="27" spans="1:26">
+      <c r="A27" s="1">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
         <v>50</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>78</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>81</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>107</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>135</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>190.375</v>
       </c>
-      <c r="G27" s="2">
-        <v>46178.491979166669</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="H27" s="2">
+        <v>46178.49197916667</v>
+      </c>
+      <c r="I27" t="s">
         <v>163</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>191</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>163</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>202</v>
-      </c>
-      <c r="L27" t="s">
-        <v>228</v>
       </c>
       <c r="M27" t="s">
         <v>228</v>
       </c>
       <c r="N27" t="s">
+        <v>228</v>
+      </c>
+      <c r="O27" t="s">
         <v>163</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>233</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>234</v>
       </c>
-      <c r="R27" t="s">
+      <c r="S27" t="s">
         <v>235</v>
       </c>
-      <c r="S27" t="s">
+      <c r="T27" t="s">
         <v>239</v>
       </c>
-      <c r="T27" t="s">
+      <c r="U27" t="s">
+        <v>241</v>
+      </c>
+      <c r="V27" t="s">
+        <v>191</v>
+      </c>
+      <c r="W27" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26">
+      <c r="A28" s="1">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28">
+        <v>21.961</v>
+      </c>
+      <c r="H28" s="2">
+        <v>46178.49200231482</v>
+      </c>
+      <c r="I28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J28" t="s">
+        <v>192</v>
+      </c>
+      <c r="K28" t="s">
+        <v>164</v>
+      </c>
+      <c r="L28" t="s">
         <v>202</v>
-      </c>
-      <c r="U27" t="s">
-        <v>191</v>
-      </c>
-      <c r="V27" t="s">
-        <v>266</v>
-      </c>
-      <c r="X27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" t="s">
-        <v>136</v>
-      </c>
-      <c r="F28">
-        <v>21.960999999999999</v>
-      </c>
-      <c r="G28" s="2">
-        <v>46178.492002314822</v>
-      </c>
-      <c r="H28" t="s">
-        <v>164</v>
-      </c>
-      <c r="I28" t="s">
-        <v>192</v>
-      </c>
-      <c r="J28" t="s">
-        <v>164</v>
-      </c>
-      <c r="K28" t="s">
-        <v>202</v>
-      </c>
-      <c r="L28" t="s">
-        <v>229</v>
       </c>
       <c r="M28" t="s">
         <v>229</v>
       </c>
       <c r="N28" t="s">
+        <v>229</v>
+      </c>
+      <c r="O28" t="s">
         <v>164</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>233</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>234</v>
       </c>
-      <c r="R28" t="s">
+      <c r="S28" t="s">
         <v>235</v>
       </c>
-      <c r="S28" t="s">
+      <c r="T28" t="s">
         <v>240</v>
       </c>
-      <c r="T28" t="s">
-        <v>202</v>
-      </c>
       <c r="U28" t="s">
+        <v>241</v>
+      </c>
+      <c r="V28" t="s">
         <v>192</v>
       </c>
-      <c r="V28" t="s">
-        <v>267</v>
-      </c>
-      <c r="X28" t="b">
-        <v>0</v>
+      <c r="W28" t="s">
+        <v>268</v>
       </c>
       <c r="Y28" t="b">
         <v>0</v>
       </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="29" spans="1:26">
+      <c r="A29" s="1">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
         <v>52</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>80</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>81</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>109</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>137</v>
       </c>
-      <c r="F29">
-        <v>138.71899999999999</v>
-      </c>
-      <c r="G29" s="2">
+      <c r="G29">
+        <v>138.719</v>
+      </c>
+      <c r="H29" s="2">
         <v>46178.4921412037</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>165</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>193</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>165</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>200</v>
-      </c>
-      <c r="L29" t="s">
-        <v>230</v>
       </c>
       <c r="M29" t="s">
         <v>230</v>
       </c>
       <c r="N29" t="s">
+        <v>230</v>
+      </c>
+      <c r="O29" t="s">
         <v>165</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>233</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>234</v>
       </c>
-      <c r="R29" t="s">
+      <c r="S29" t="s">
         <v>235</v>
       </c>
-      <c r="S29" t="s">
+      <c r="T29" t="s">
         <v>236</v>
       </c>
-      <c r="T29" t="s">
-        <v>200</v>
-      </c>
       <c r="U29" t="s">
+        <v>241</v>
+      </c>
+      <c r="V29" t="s">
         <v>193</v>
       </c>
-      <c r="V29" t="s">
-        <v>268</v>
-      </c>
-      <c r="X29" t="b">
-        <v>0</v>
+      <c r="W29" t="s">
+        <v>269</v>
       </c>
       <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
         <v>0</v>
       </c>
     </row>

--- a/excel/Salida.xlsx
+++ b/excel/Salida.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="272">
   <si>
     <t>file_name</t>
   </si>
@@ -499,7 +499,7 @@
     <t>CL_MLP_PAO_IF_Ortho_26_05_15_ev1</t>
   </si>
   <si>
-    <t>CL_MLP_PAO_IF_Ortho_26_05_15_estacion_cabecera</t>
+    <t>CL_MLP_PAO_IF_Ortho_26_05_15_Estacion_Cabecera</t>
   </si>
   <si>
     <t>CL_MLP_PAO_IF_Ortho_26_05_16_torres_e48_a_e84</t>
@@ -583,7 +583,7 @@
     <t>CL_MLP_PAO_IF_Ortho_26_05_15_ev1.tif</t>
   </si>
   <si>
-    <t>CL_MLP_PAO_IF_Ortho_26_05_15_estacion_cabecera.tif</t>
+    <t>CL_MLP_PAO_IF_Ortho_26_05_15_Estacion_Cabecera.tif</t>
   </si>
   <si>
     <t>CL_MLP_PAO_IF_Ortho_26_05_16_torres_e48_a_e84.tif</t>
@@ -694,7 +694,7 @@
     <t>ev1</t>
   </si>
   <si>
-    <t>estacion_cabecera</t>
+    <t>Estacion_Cabecera</t>
   </si>
   <si>
     <t>torres_e48_a_e84</t>
@@ -712,9 +712,15 @@
     <t>estacion_cabeceras|estacion_cabecera</t>
   </si>
   <si>
+    <t>Estacion_Cabecera|estacion_cabecera</t>
+  </si>
+  <si>
     <t>CL_MLP_PAO_IF_Ortho_26_05_01_estacion_cabeceras|CL_MLP_PAO_IF_Ortho_26_05_01_estacion_cabecera</t>
   </si>
   <si>
+    <t>CL_MLP_PAO_IF_Ortho_26_05_15_Estacion_Cabecera|CL_MLP_PAO_IF_Ortho_26_05_15_estacion_cabecera</t>
+  </si>
+  <si>
     <t>ok</t>
   </si>
   <si>
@@ -811,7 +817,7 @@
     <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_15_ev1.tif</t>
   </si>
   <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_15_estacion_cabecera.tif</t>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_15_Estacion_Cabecera.tif</t>
   </si>
   <si>
     <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_16_torres_e48_a_e84.tif</t>
@@ -1309,28 +1315,28 @@
         <v>231</v>
       </c>
       <c r="O2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="U2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V2" t="s">
         <v>166</v>
       </c>
       <c r="W2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Y2" t="b">
         <v>0</v>
@@ -1386,25 +1392,25 @@
         <v>139</v>
       </c>
       <c r="Q3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V3" t="s">
         <v>167</v>
       </c>
       <c r="W3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Y3" t="b">
         <v>0</v>
@@ -1460,25 +1466,25 @@
         <v>140</v>
       </c>
       <c r="Q4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V4" t="s">
         <v>168</v>
       </c>
       <c r="W4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
@@ -1534,25 +1540,25 @@
         <v>141</v>
       </c>
       <c r="Q5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V5" t="s">
         <v>169</v>
       </c>
       <c r="W5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
@@ -1608,25 +1614,25 @@
         <v>142</v>
       </c>
       <c r="Q6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V6" t="s">
         <v>170</v>
       </c>
       <c r="W6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
@@ -1682,25 +1688,25 @@
         <v>143</v>
       </c>
       <c r="Q7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V7" t="s">
         <v>171</v>
       </c>
       <c r="W7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Y7" t="b">
         <v>0</v>
@@ -1756,25 +1762,25 @@
         <v>144</v>
       </c>
       <c r="Q8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V8" t="s">
         <v>172</v>
       </c>
       <c r="W8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Y8" t="b">
         <v>0</v>
@@ -1830,25 +1836,25 @@
         <v>145</v>
       </c>
       <c r="Q9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V9" t="s">
         <v>173</v>
       </c>
       <c r="W9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Y9" t="b">
         <v>0</v>
@@ -1904,25 +1910,25 @@
         <v>146</v>
       </c>
       <c r="Q10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V10" t="s">
         <v>174</v>
       </c>
       <c r="W10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Y10" t="b">
         <v>0</v>
@@ -1978,25 +1984,25 @@
         <v>147</v>
       </c>
       <c r="Q11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V11" t="s">
         <v>175</v>
       </c>
       <c r="W11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Y11" t="b">
         <v>0</v>
@@ -2052,25 +2058,25 @@
         <v>148</v>
       </c>
       <c r="Q12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V12" t="s">
         <v>176</v>
       </c>
       <c r="W12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Y12" t="b">
         <v>0</v>
@@ -2126,25 +2132,25 @@
         <v>149</v>
       </c>
       <c r="Q13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V13" t="s">
         <v>177</v>
       </c>
       <c r="W13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Y13" t="b">
         <v>0</v>
@@ -2200,25 +2206,25 @@
         <v>150</v>
       </c>
       <c r="Q14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V14" t="s">
         <v>178</v>
       </c>
       <c r="W14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Y14" t="b">
         <v>0</v>
@@ -2274,25 +2280,25 @@
         <v>151</v>
       </c>
       <c r="Q15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T15" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V15" t="s">
         <v>179</v>
       </c>
       <c r="W15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Y15" t="b">
         <v>0</v>
@@ -2348,25 +2354,25 @@
         <v>152</v>
       </c>
       <c r="Q16" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R16" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S16" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T16" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V16" t="s">
         <v>180</v>
       </c>
       <c r="W16" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Y16" t="b">
         <v>0</v>
@@ -2422,25 +2428,25 @@
         <v>153</v>
       </c>
       <c r="Q17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R17" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V17" t="s">
         <v>181</v>
       </c>
       <c r="W17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y17" t="b">
         <v>0</v>
@@ -2496,25 +2502,25 @@
         <v>154</v>
       </c>
       <c r="Q18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S18" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T18" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U18" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V18" t="s">
         <v>182</v>
       </c>
       <c r="W18" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Y18" t="b">
         <v>0</v>
@@ -2570,25 +2576,25 @@
         <v>155</v>
       </c>
       <c r="Q19" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R19" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S19" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T19" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V19" t="s">
         <v>183</v>
       </c>
       <c r="W19" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y19" t="b">
         <v>0</v>
@@ -2644,25 +2650,25 @@
         <v>156</v>
       </c>
       <c r="Q20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S20" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T20" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V20" t="s">
         <v>184</v>
       </c>
       <c r="W20" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Y20" t="b">
         <v>0</v>
@@ -2718,25 +2724,25 @@
         <v>157</v>
       </c>
       <c r="Q21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R21" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T21" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V21" t="s">
         <v>185</v>
       </c>
       <c r="W21" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Y21" t="b">
         <v>0</v>
@@ -2792,25 +2798,25 @@
         <v>158</v>
       </c>
       <c r="Q22" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S22" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T22" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U22" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V22" t="s">
         <v>186</v>
       </c>
       <c r="W22" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y22" t="b">
         <v>0</v>
@@ -2866,25 +2872,25 @@
         <v>159</v>
       </c>
       <c r="Q23" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R23" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S23" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T23" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="U23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V23" t="s">
         <v>187</v>
       </c>
       <c r="W23" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Y23" t="b">
         <v>0</v>
@@ -2940,25 +2946,25 @@
         <v>160</v>
       </c>
       <c r="Q24" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R24" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T24" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U24" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V24" t="s">
         <v>188</v>
       </c>
       <c r="W24" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Y24" t="b">
         <v>0</v>
@@ -3008,31 +3014,31 @@
         <v>226</v>
       </c>
       <c r="N25" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="O25" t="s">
-        <v>161</v>
+        <v>234</v>
       </c>
       <c r="Q25" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R25" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S25" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T25" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="U25" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V25" t="s">
         <v>189</v>
       </c>
       <c r="W25" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Y25" t="b">
         <v>0</v>
@@ -3088,25 +3094,25 @@
         <v>162</v>
       </c>
       <c r="Q26" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R26" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T26" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U26" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V26" t="s">
         <v>190</v>
       </c>
       <c r="W26" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Y26" t="b">
         <v>0</v>
@@ -3162,25 +3168,25 @@
         <v>163</v>
       </c>
       <c r="Q27" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R27" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S27" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T27" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U27" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V27" t="s">
         <v>191</v>
       </c>
       <c r="W27" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Y27" t="b">
         <v>0</v>
@@ -3236,25 +3242,25 @@
         <v>164</v>
       </c>
       <c r="Q28" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S28" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T28" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="U28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V28" t="s">
         <v>192</v>
       </c>
       <c r="W28" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Y28" t="b">
         <v>0</v>
@@ -3310,25 +3316,25 @@
         <v>165</v>
       </c>
       <c r="Q29" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R29" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T29" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="U29" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V29" t="s">
         <v>193</v>
       </c>
       <c r="W29" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Y29" t="b">
         <v>0</v>

--- a/excel/Salida.xlsx
+++ b/excel/Salida.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="270">
   <si>
     <t>file_name</t>
   </si>
@@ -430,7 +430,7 @@
     <t>SOLO_TIF_19May26\GEOSP-TRN-002660_GS_ORTOFOTO_EM1_150526.tif</t>
   </si>
   <si>
-    <t>CL_MLP_PAO_IF_Ortho_26_05_01_estacion_cabeceras</t>
+    <t>CL_MLP_PAO_IF_Ortho_26_05_01_Estacion_Cabecera</t>
   </si>
   <si>
     <t>CL_MLP_PAO_IF_Ortho_26_05_06_eb3</t>
@@ -514,7 +514,7 @@
     <t>CL_MLP_PAO_IF_Ortho_26_05_15_em1</t>
   </si>
   <si>
-    <t>CL_MLP_PAO_IF_Ortho_26_05_01_estacion_cabeceras.tif</t>
+    <t>CL_MLP_PAO_IF_Ortho_26_05_01_Estacion_Cabecera.tif</t>
   </si>
   <si>
     <t>CL_MLP_PAO_IF_Ortho_26_05_06_eb3.tif</t>
@@ -625,7 +625,7 @@
     <t>26_05_17</t>
   </si>
   <si>
-    <t>estacion_cabeceras</t>
+    <t>Estacion_Cabecera</t>
   </si>
   <si>
     <t>eb3</t>
@@ -694,9 +694,6 @@
     <t>ev1</t>
   </si>
   <si>
-    <t>Estacion_Cabecera</t>
-  </si>
-  <si>
     <t>torres_e48_a_e84</t>
   </si>
   <si>
@@ -709,13 +706,10 @@
     <t>em1</t>
   </si>
   <si>
-    <t>estacion_cabeceras|estacion_cabecera</t>
-  </si>
-  <si>
     <t>Estacion_Cabecera|estacion_cabecera</t>
   </si>
   <si>
-    <t>CL_MLP_PAO_IF_Ortho_26_05_01_estacion_cabeceras|CL_MLP_PAO_IF_Ortho_26_05_01_estacion_cabecera</t>
+    <t>CL_MLP_PAO_IF_Ortho_26_05_01_Estacion_Cabecera|CL_MLP_PAO_IF_Ortho_26_05_01_estacion_cabecera</t>
   </si>
   <si>
     <t>CL_MLP_PAO_IF_Ortho_26_05_15_Estacion_Cabecera|CL_MLP_PAO_IF_Ortho_26_05_15_estacion_cabecera</t>
@@ -748,7 +742,7 @@
     <t>26_05</t>
   </si>
   <si>
-    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_01_estacion_cabeceras.tif</t>
+    <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\Chacay_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_01_Estacion_Cabecera.tif</t>
   </si>
   <si>
     <t>\\amssclgis10.ams.gmams.cl\CL_MLP_PAO\El_Mauro_Drone\26_05\CL_MLP_PAO_IF_Ortho_26_05_06_eb3.tif</t>
@@ -1312,31 +1306,31 @@
         <v>203</v>
       </c>
       <c r="N2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O2" t="s">
         <v>231</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>233</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
+        <v>234</v>
+      </c>
+      <c r="S2" t="s">
         <v>235</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>236</v>
       </c>
-      <c r="S2" t="s">
-        <v>237</v>
-      </c>
-      <c r="T2" t="s">
-        <v>238</v>
-      </c>
       <c r="U2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V2" t="s">
         <v>166</v>
       </c>
       <c r="W2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="Y2" t="b">
         <v>0</v>
@@ -1392,25 +1386,25 @@
         <v>139</v>
       </c>
       <c r="Q3" t="s">
+        <v>233</v>
+      </c>
+      <c r="R3" t="s">
+        <v>234</v>
+      </c>
+      <c r="S3" t="s">
         <v>235</v>
       </c>
-      <c r="R3" t="s">
-        <v>236</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>237</v>
       </c>
-      <c r="T3" t="s">
-        <v>239</v>
-      </c>
       <c r="U3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V3" t="s">
         <v>167</v>
       </c>
       <c r="W3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Y3" t="b">
         <v>0</v>
@@ -1466,25 +1460,25 @@
         <v>140</v>
       </c>
       <c r="Q4" t="s">
+        <v>233</v>
+      </c>
+      <c r="R4" t="s">
+        <v>234</v>
+      </c>
+      <c r="S4" t="s">
         <v>235</v>
       </c>
-      <c r="R4" t="s">
-        <v>236</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>237</v>
       </c>
-      <c r="T4" t="s">
-        <v>239</v>
-      </c>
       <c r="U4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V4" t="s">
         <v>168</v>
       </c>
       <c r="W4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
@@ -1540,25 +1534,25 @@
         <v>141</v>
       </c>
       <c r="Q5" t="s">
+        <v>233</v>
+      </c>
+      <c r="R5" t="s">
+        <v>234</v>
+      </c>
+      <c r="S5" t="s">
         <v>235</v>
       </c>
-      <c r="R5" t="s">
-        <v>236</v>
-      </c>
-      <c r="S5" t="s">
-        <v>237</v>
-      </c>
       <c r="T5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V5" t="s">
         <v>169</v>
       </c>
       <c r="W5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
@@ -1614,25 +1608,25 @@
         <v>142</v>
       </c>
       <c r="Q6" t="s">
+        <v>233</v>
+      </c>
+      <c r="R6" t="s">
+        <v>234</v>
+      </c>
+      <c r="S6" t="s">
         <v>235</v>
       </c>
-      <c r="R6" t="s">
-        <v>236</v>
-      </c>
-      <c r="S6" t="s">
-        <v>237</v>
-      </c>
       <c r="T6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V6" t="s">
         <v>170</v>
       </c>
       <c r="W6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
@@ -1688,25 +1682,25 @@
         <v>143</v>
       </c>
       <c r="Q7" t="s">
+        <v>233</v>
+      </c>
+      <c r="R7" t="s">
+        <v>234</v>
+      </c>
+      <c r="S7" t="s">
         <v>235</v>
       </c>
-      <c r="R7" t="s">
-        <v>236</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>237</v>
       </c>
-      <c r="T7" t="s">
-        <v>239</v>
-      </c>
       <c r="U7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V7" t="s">
         <v>171</v>
       </c>
       <c r="W7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Y7" t="b">
         <v>0</v>
@@ -1762,25 +1756,25 @@
         <v>144</v>
       </c>
       <c r="Q8" t="s">
+        <v>233</v>
+      </c>
+      <c r="R8" t="s">
+        <v>234</v>
+      </c>
+      <c r="S8" t="s">
         <v>235</v>
       </c>
-      <c r="R8" t="s">
-        <v>236</v>
-      </c>
-      <c r="S8" t="s">
-        <v>237</v>
-      </c>
       <c r="T8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V8" t="s">
         <v>172</v>
       </c>
       <c r="W8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="Y8" t="b">
         <v>0</v>
@@ -1836,25 +1830,25 @@
         <v>145</v>
       </c>
       <c r="Q9" t="s">
+        <v>233</v>
+      </c>
+      <c r="R9" t="s">
+        <v>234</v>
+      </c>
+      <c r="S9" t="s">
         <v>235</v>
       </c>
-      <c r="R9" t="s">
-        <v>236</v>
-      </c>
-      <c r="S9" t="s">
-        <v>237</v>
-      </c>
       <c r="T9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V9" t="s">
         <v>173</v>
       </c>
       <c r="W9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Y9" t="b">
         <v>0</v>
@@ -1910,25 +1904,25 @@
         <v>146</v>
       </c>
       <c r="Q10" t="s">
+        <v>233</v>
+      </c>
+      <c r="R10" t="s">
+        <v>234</v>
+      </c>
+      <c r="S10" t="s">
         <v>235</v>
       </c>
-      <c r="R10" t="s">
-        <v>236</v>
-      </c>
-      <c r="S10" t="s">
-        <v>237</v>
-      </c>
       <c r="T10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V10" t="s">
         <v>174</v>
       </c>
       <c r="W10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Y10" t="b">
         <v>0</v>
@@ -1984,25 +1978,25 @@
         <v>147</v>
       </c>
       <c r="Q11" t="s">
+        <v>233</v>
+      </c>
+      <c r="R11" t="s">
+        <v>234</v>
+      </c>
+      <c r="S11" t="s">
         <v>235</v>
       </c>
-      <c r="R11" t="s">
-        <v>236</v>
-      </c>
-      <c r="S11" t="s">
-        <v>237</v>
-      </c>
       <c r="T11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V11" t="s">
         <v>175</v>
       </c>
       <c r="W11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Y11" t="b">
         <v>0</v>
@@ -2058,25 +2052,25 @@
         <v>148</v>
       </c>
       <c r="Q12" t="s">
+        <v>233</v>
+      </c>
+      <c r="R12" t="s">
+        <v>234</v>
+      </c>
+      <c r="S12" t="s">
         <v>235</v>
       </c>
-      <c r="R12" t="s">
-        <v>236</v>
-      </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>237</v>
       </c>
-      <c r="T12" t="s">
-        <v>239</v>
-      </c>
       <c r="U12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V12" t="s">
         <v>176</v>
       </c>
       <c r="W12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y12" t="b">
         <v>0</v>
@@ -2132,25 +2126,25 @@
         <v>149</v>
       </c>
       <c r="Q13" t="s">
+        <v>233</v>
+      </c>
+      <c r="R13" t="s">
+        <v>234</v>
+      </c>
+      <c r="S13" t="s">
         <v>235</v>
       </c>
-      <c r="R13" t="s">
-        <v>236</v>
-      </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
         <v>237</v>
       </c>
-      <c r="T13" t="s">
-        <v>239</v>
-      </c>
       <c r="U13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V13" t="s">
         <v>177</v>
       </c>
       <c r="W13" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Y13" t="b">
         <v>0</v>
@@ -2206,25 +2200,25 @@
         <v>150</v>
       </c>
       <c r="Q14" t="s">
+        <v>233</v>
+      </c>
+      <c r="R14" t="s">
+        <v>234</v>
+      </c>
+      <c r="S14" t="s">
         <v>235</v>
       </c>
-      <c r="R14" t="s">
-        <v>236</v>
-      </c>
-      <c r="S14" t="s">
-        <v>237</v>
-      </c>
       <c r="T14" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V14" t="s">
         <v>178</v>
       </c>
       <c r="W14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Y14" t="b">
         <v>0</v>
@@ -2280,25 +2274,25 @@
         <v>151</v>
       </c>
       <c r="Q15" t="s">
+        <v>233</v>
+      </c>
+      <c r="R15" t="s">
+        <v>234</v>
+      </c>
+      <c r="S15" t="s">
         <v>235</v>
       </c>
-      <c r="R15" t="s">
-        <v>236</v>
-      </c>
-      <c r="S15" t="s">
-        <v>237</v>
-      </c>
       <c r="T15" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U15" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V15" t="s">
         <v>179</v>
       </c>
       <c r="W15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Y15" t="b">
         <v>0</v>
@@ -2354,25 +2348,25 @@
         <v>152</v>
       </c>
       <c r="Q16" t="s">
+        <v>233</v>
+      </c>
+      <c r="R16" t="s">
+        <v>234</v>
+      </c>
+      <c r="S16" t="s">
         <v>235</v>
       </c>
-      <c r="R16" t="s">
-        <v>236</v>
-      </c>
-      <c r="S16" t="s">
+      <c r="T16" t="s">
         <v>237</v>
       </c>
-      <c r="T16" t="s">
-        <v>239</v>
-      </c>
       <c r="U16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V16" t="s">
         <v>180</v>
       </c>
       <c r="W16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Y16" t="b">
         <v>0</v>
@@ -2428,25 +2422,25 @@
         <v>153</v>
       </c>
       <c r="Q17" t="s">
+        <v>233</v>
+      </c>
+      <c r="R17" t="s">
+        <v>234</v>
+      </c>
+      <c r="S17" t="s">
         <v>235</v>
       </c>
-      <c r="R17" t="s">
-        <v>236</v>
-      </c>
-      <c r="S17" t="s">
-        <v>237</v>
-      </c>
       <c r="T17" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U17" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V17" t="s">
         <v>181</v>
       </c>
       <c r="W17" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Y17" t="b">
         <v>0</v>
@@ -2502,25 +2496,25 @@
         <v>154</v>
       </c>
       <c r="Q18" t="s">
+        <v>233</v>
+      </c>
+      <c r="R18" t="s">
+        <v>234</v>
+      </c>
+      <c r="S18" t="s">
         <v>235</v>
       </c>
-      <c r="R18" t="s">
-        <v>236</v>
-      </c>
-      <c r="S18" t="s">
+      <c r="T18" t="s">
         <v>237</v>
       </c>
-      <c r="T18" t="s">
-        <v>239</v>
-      </c>
       <c r="U18" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V18" t="s">
         <v>182</v>
       </c>
       <c r="W18" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Y18" t="b">
         <v>0</v>
@@ -2576,25 +2570,25 @@
         <v>155</v>
       </c>
       <c r="Q19" t="s">
+        <v>233</v>
+      </c>
+      <c r="R19" t="s">
+        <v>234</v>
+      </c>
+      <c r="S19" t="s">
         <v>235</v>
       </c>
-      <c r="R19" t="s">
-        <v>236</v>
-      </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
         <v>237</v>
       </c>
-      <c r="T19" t="s">
-        <v>239</v>
-      </c>
       <c r="U19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V19" t="s">
         <v>183</v>
       </c>
       <c r="W19" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Y19" t="b">
         <v>0</v>
@@ -2650,25 +2644,25 @@
         <v>156</v>
       </c>
       <c r="Q20" t="s">
+        <v>233</v>
+      </c>
+      <c r="R20" t="s">
+        <v>234</v>
+      </c>
+      <c r="S20" t="s">
         <v>235</v>
       </c>
-      <c r="R20" t="s">
-        <v>236</v>
-      </c>
-      <c r="S20" t="s">
-        <v>237</v>
-      </c>
       <c r="T20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V20" t="s">
         <v>184</v>
       </c>
       <c r="W20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Y20" t="b">
         <v>0</v>
@@ -2724,25 +2718,25 @@
         <v>157</v>
       </c>
       <c r="Q21" t="s">
+        <v>233</v>
+      </c>
+      <c r="R21" t="s">
+        <v>234</v>
+      </c>
+      <c r="S21" t="s">
         <v>235</v>
       </c>
-      <c r="R21" t="s">
-        <v>236</v>
-      </c>
-      <c r="S21" t="s">
-        <v>237</v>
-      </c>
       <c r="T21" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U21" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V21" t="s">
         <v>185</v>
       </c>
       <c r="W21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Y21" t="b">
         <v>0</v>
@@ -2798,25 +2792,25 @@
         <v>158</v>
       </c>
       <c r="Q22" t="s">
+        <v>233</v>
+      </c>
+      <c r="R22" t="s">
+        <v>234</v>
+      </c>
+      <c r="S22" t="s">
         <v>235</v>
       </c>
-      <c r="R22" t="s">
-        <v>236</v>
-      </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>237</v>
       </c>
-      <c r="T22" t="s">
-        <v>239</v>
-      </c>
       <c r="U22" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V22" t="s">
         <v>186</v>
       </c>
       <c r="W22" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y22" t="b">
         <v>0</v>
@@ -2872,25 +2866,25 @@
         <v>159</v>
       </c>
       <c r="Q23" t="s">
+        <v>233</v>
+      </c>
+      <c r="R23" t="s">
+        <v>234</v>
+      </c>
+      <c r="S23" t="s">
         <v>235</v>
       </c>
-      <c r="R23" t="s">
-        <v>236</v>
-      </c>
-      <c r="S23" t="s">
+      <c r="T23" t="s">
         <v>237</v>
       </c>
-      <c r="T23" t="s">
-        <v>239</v>
-      </c>
       <c r="U23" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V23" t="s">
         <v>187</v>
       </c>
       <c r="W23" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Y23" t="b">
         <v>0</v>
@@ -2946,25 +2940,25 @@
         <v>160</v>
       </c>
       <c r="Q24" t="s">
+        <v>233</v>
+      </c>
+      <c r="R24" t="s">
+        <v>234</v>
+      </c>
+      <c r="S24" t="s">
         <v>235</v>
       </c>
-      <c r="R24" t="s">
-        <v>236</v>
-      </c>
-      <c r="S24" t="s">
-        <v>237</v>
-      </c>
       <c r="T24" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V24" t="s">
         <v>188</v>
       </c>
       <c r="W24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Y24" t="b">
         <v>0</v>
@@ -3011,34 +3005,34 @@
         <v>200</v>
       </c>
       <c r="M25" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="N25" t="s">
+        <v>230</v>
+      </c>
+      <c r="O25" t="s">
         <v>232</v>
       </c>
-      <c r="O25" t="s">
+      <c r="Q25" t="s">
+        <v>233</v>
+      </c>
+      <c r="R25" t="s">
         <v>234</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="S25" t="s">
         <v>235</v>
       </c>
-      <c r="R25" t="s">
+      <c r="T25" t="s">
         <v>236</v>
       </c>
-      <c r="S25" t="s">
-        <v>237</v>
-      </c>
-      <c r="T25" t="s">
-        <v>238</v>
-      </c>
       <c r="U25" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V25" t="s">
         <v>189</v>
       </c>
       <c r="W25" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Y25" t="b">
         <v>0</v>
@@ -3085,34 +3079,34 @@
         <v>201</v>
       </c>
       <c r="M26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O26" t="s">
         <v>162</v>
       </c>
       <c r="Q26" t="s">
+        <v>233</v>
+      </c>
+      <c r="R26" t="s">
+        <v>234</v>
+      </c>
+      <c r="S26" t="s">
         <v>235</v>
       </c>
-      <c r="R26" t="s">
-        <v>236</v>
-      </c>
-      <c r="S26" t="s">
-        <v>237</v>
-      </c>
       <c r="T26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V26" t="s">
         <v>190</v>
       </c>
       <c r="W26" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Y26" t="b">
         <v>0</v>
@@ -3159,34 +3153,34 @@
         <v>202</v>
       </c>
       <c r="M27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O27" t="s">
         <v>163</v>
       </c>
       <c r="Q27" t="s">
+        <v>233</v>
+      </c>
+      <c r="R27" t="s">
+        <v>234</v>
+      </c>
+      <c r="S27" t="s">
         <v>235</v>
       </c>
-      <c r="R27" t="s">
-        <v>236</v>
-      </c>
-      <c r="S27" t="s">
-        <v>237</v>
-      </c>
       <c r="T27" t="s">
+        <v>239</v>
+      </c>
+      <c r="U27" t="s">
         <v>241</v>
-      </c>
-      <c r="U27" t="s">
-        <v>243</v>
       </c>
       <c r="V27" t="s">
         <v>191</v>
       </c>
       <c r="W27" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Y27" t="b">
         <v>0</v>
@@ -3233,34 +3227,34 @@
         <v>202</v>
       </c>
       <c r="M28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O28" t="s">
         <v>164</v>
       </c>
       <c r="Q28" t="s">
+        <v>233</v>
+      </c>
+      <c r="R28" t="s">
+        <v>234</v>
+      </c>
+      <c r="S28" t="s">
         <v>235</v>
       </c>
-      <c r="R28" t="s">
-        <v>236</v>
-      </c>
-      <c r="S28" t="s">
-        <v>237</v>
-      </c>
       <c r="T28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="U28" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V28" t="s">
         <v>192</v>
       </c>
       <c r="W28" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Y28" t="b">
         <v>0</v>
@@ -3307,34 +3301,34 @@
         <v>200</v>
       </c>
       <c r="M29" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N29" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O29" t="s">
         <v>165</v>
       </c>
       <c r="Q29" t="s">
+        <v>233</v>
+      </c>
+      <c r="R29" t="s">
+        <v>234</v>
+      </c>
+      <c r="S29" t="s">
         <v>235</v>
       </c>
-      <c r="R29" t="s">
+      <c r="T29" t="s">
         <v>236</v>
       </c>
-      <c r="S29" t="s">
-        <v>237</v>
-      </c>
-      <c r="T29" t="s">
-        <v>238</v>
-      </c>
       <c r="U29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V29" t="s">
         <v>193</v>
       </c>
       <c r="W29" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Y29" t="b">
         <v>0</v>
